--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -15800,8 +15800,7 @@
       "displayedAt": "2026-10-12T16:10:00+09:00",
       "closedAt": "2026-10-12T16:20:00+09:00",
       "answers": [
-        { "questionId": 301, "optionIds": [3001], "textAnswer": null },
-        { "questionId": 302, "optionIds": [], "textAnswer": "주관식 답변" }
+        { "questionId": 301, "optionIds": [3001], "textAnswer": null }
       ],
       "score": 100,
       "passed": true,

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -3534,6 +3534,7 @@
       <x:c r="A36" s="678" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">• displayStartAt / displayEndAt 및 period/repeat 계열은 WPF 목록 응답에서 제거.
+• IMAGE content.linkUrl(이미지 클릭 시 URL 열기) 삭제. 모든 이미지 모드에서 클릭 동작 없음.
 • footerAction / footerLinkUrl은 content가 아니라 popups[] 최상위.
 • useBackgroundOverlay / backgroundOverlayOpacity / popupPosition / headerFontSize / bodyFontSize / footerFontSize도 popups[] 최상위.
 • showCloseButton legacy 수신 제거, showFooterButton만 사용.
@@ -8070,48 +8071,34 @@
       <x:c r="H12" s="300"/>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="666" t="str">
+      <x:c r="A13" s="695" t="str">
         <x:v>keepAspectRatio</x:v>
       </x:c>
-      <x:c r="B13" s="385" t="str">
+      <x:c r="B13" s="668" t="str">
         <x:v>popups[].content.keepAspectRatio</x:v>
       </x:c>
-      <x:c r="C13" s="385" t="str">
+      <x:c r="C13" s="668" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="D13" s="385" t="str">
+      <x:c r="D13" s="668" t="str">
         <x:v>true</x:v>
       </x:c>
-      <x:c r="E13" s="385" t="str">
+      <x:c r="E13" s="668" t="str">
         <x:v>비율 유지</x:v>
       </x:c>
-      <x:c r="F13" s="667" t="str">
+      <x:c r="F13" s="669" t="str">
         <x:v>FIT_TO_IMAGE</x:v>
       </x:c>
       <x:c r="G13" s="300"/>
       <x:c r="H13" s="300"/>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="695" t="str">
-        <x:v>linkUrl</x:v>
-      </x:c>
-      <x:c r="B14" s="668" t="str">
-        <x:v>popups[].content.linkUrl</x:v>
-      </x:c>
-      <x:c r="C14" s="668" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="D14" s="668" t="str">
-        <x:v>""</x:v>
-      </x:c>
-      <x:c r="E14" s="668" t="str">
-        <x:v>이미지 클릭 링크</x:v>
-      </x:c>
-      <x:c r="F14" s="669" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ORIGINAL 모드에서만 사용(ADAPTIVE·FIT_TO_IMAGE 미사용)</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A14" s="300"/>
+      <x:c r="B14" s="300"/>
+      <x:c r="C14" s="300"/>
+      <x:c r="D14" s="300"/>
+      <x:c r="E14" s="300"/>
+      <x:c r="F14" s="300"/>
       <x:c r="G14" s="300"/>
       <x:c r="H14" s="300"/>
     </x:row>

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -6298,219 +6298,190 @@
       <x:c r="H17" s="300"/>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="771" t="str">
-        <x:v>contentTitle</x:v>
-      </x:c>
-      <x:c r="B18" s="772" t="str">
-        <x:v>popups[].content.contentTitle</x:v>
-      </x:c>
-      <x:c r="C18" s="772" t="str">
+      <x:c r="A18" s="666" t="str">
+        <x:v>highlightText</x:v>
+      </x:c>
+      <x:c r="B18" s="385" t="str">
+        <x:v>popups[].content.highlightText</x:v>
+      </x:c>
+      <x:c r="C18" s="385" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="D18" s="772" t="str">
+      <x:c r="D18" s="385" t="str">
         <x:v>""</x:v>
       </x:c>
-      <x:c r="E18" s="772" t="str">
-        <x:v>콘텐츠 내부 제목</x:v>
-      </x:c>
-      <x:c r="F18" s="773" t="str"/>
+      <x:c r="E18" s="385" t="str">
+        <x:v>강조 문구</x:v>
+      </x:c>
+      <x:c r="F18" s="667" t="str"/>
       <x:c r="G18" s="300"/>
       <x:c r="H18" s="300"/>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
-      <x:c r="A19" s="771" t="str">
-        <x:v>showContentHeader</x:v>
-      </x:c>
-      <x:c r="B19" s="772" t="str">
-        <x:v>popups[].content.showContentHeader</x:v>
-      </x:c>
-      <x:c r="C19" s="772" t="str">
+      <x:c r="A19" s="666" t="str">
+        <x:v>showHighlight</x:v>
+      </x:c>
+      <x:c r="B19" s="385" t="str">
+        <x:v>popups[].content.showHighlight</x:v>
+      </x:c>
+      <x:c r="C19" s="385" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="D19" s="772" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="E19" s="772" t="str">
-        <x:v>내부 제목/설명 영역 표시</x:v>
-      </x:c>
-      <x:c r="F19" s="773" t="str"/>
+      <x:c r="D19" s="385" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="E19" s="385" t="str">
+        <x:v>강조 영역 표시</x:v>
+      </x:c>
+      <x:c r="F19" s="667" t="str">
+        <x:v>문구 존재로 자동 추정하지 않음</x:v>
+      </x:c>
       <x:c r="G19" s="300"/>
       <x:c r="H19" s="300"/>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="771" t="str">
-        <x:v>description</x:v>
-      </x:c>
-      <x:c r="B20" s="772" t="str">
-        <x:v>popups[].content.description</x:v>
-      </x:c>
-      <x:c r="C20" s="772" t="str">
+      <x:c r="A20" s="666" t="str">
+        <x:v>bottomDescription</x:v>
+      </x:c>
+      <x:c r="B20" s="385" t="str">
+        <x:v>popups[].content.bottomDescription</x:v>
+      </x:c>
+      <x:c r="C20" s="385" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="D20" s="772" t="str">
+      <x:c r="D20" s="385" t="str">
         <x:v>""</x:v>
       </x:c>
-      <x:c r="E20" s="772" t="str">
-        <x:v>콘텐츠 설명</x:v>
-      </x:c>
-      <x:c r="F20" s="773" t="str"/>
+      <x:c r="E20" s="385" t="str">
+        <x:v>하단 설명</x:v>
+      </x:c>
+      <x:c r="F20" s="667" t="str"/>
       <x:c r="G20" s="300"/>
       <x:c r="H20" s="300"/>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="666" t="str">
-        <x:v>highlightText</x:v>
+        <x:v>bottomDescriptionUrl</x:v>
       </x:c>
       <x:c r="B21" s="385" t="str">
-        <x:v>popups[].content.highlightText</x:v>
+        <x:v>popups[].content.bottomDescriptionUrl</x:v>
       </x:c>
       <x:c r="C21" s="385" t="str">
-        <x:v>N</x:v>
+        <x:v>조건부</x:v>
       </x:c>
       <x:c r="D21" s="385" t="str">
         <x:v>""</x:v>
       </x:c>
       <x:c r="E21" s="385" t="str">
-        <x:v>강조 문구</x:v>
+        <x:v>하단 설명 링크</x:v>
       </x:c>
       <x:c r="F21" s="667" t="str"/>
       <x:c r="G21" s="300"/>
       <x:c r="H21" s="300"/>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="666" t="str">
-        <x:v>showHighlight</x:v>
-      </x:c>
-      <x:c r="B22" s="385" t="str">
-        <x:v>popups[].content.showHighlight</x:v>
-      </x:c>
-      <x:c r="C22" s="385" t="str">
+      <x:c r="A22" s="695" t="str">
+        <x:v>showBottomDescription</x:v>
+      </x:c>
+      <x:c r="B22" s="668" t="str">
+        <x:v>popups[].content.showBottomDescription</x:v>
+      </x:c>
+      <x:c r="C22" s="668" t="str">
         <x:v>N</x:v>
       </x:c>
-      <x:c r="D22" s="385" t="str">
+      <x:c r="D22" s="668" t="str">
         <x:v>false</x:v>
       </x:c>
-      <x:c r="E22" s="385" t="str">
-        <x:v>강조 영역 표시</x:v>
-      </x:c>
-      <x:c r="F22" s="667" t="str">
-        <x:v>문구 존재로 자동 추정하지 않음</x:v>
-      </x:c>
+      <x:c r="E22" s="668" t="str">
+        <x:v>하단 설명 표시</x:v>
+      </x:c>
+      <x:c r="F22" s="669" t="str"/>
       <x:c r="G22" s="300"/>
       <x:c r="H22" s="300"/>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
-      <x:c r="A23" s="666" t="str">
-        <x:v>bottomDescription</x:v>
-      </x:c>
-      <x:c r="B23" s="385" t="str">
-        <x:v>popups[].content.bottomDescription</x:v>
-      </x:c>
-      <x:c r="C23" s="385" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="D23" s="385" t="str">
-        <x:v>""</x:v>
-      </x:c>
-      <x:c r="E23" s="385" t="str">
-        <x:v>하단 설명</x:v>
-      </x:c>
-      <x:c r="F23" s="667" t="str"/>
+      <x:c r="A23" s="300"/>
+      <x:c r="B23" s="300"/>
+      <x:c r="C23" s="300"/>
+      <x:c r="D23" s="300"/>
+      <x:c r="E23" s="300"/>
+      <x:c r="F23" s="300"/>
       <x:c r="G23" s="300"/>
       <x:c r="H23" s="300"/>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="666" t="str">
-        <x:v>bottomDescriptionUrl</x:v>
-      </x:c>
-      <x:c r="B24" s="385" t="str">
-        <x:v>popups[].content.bottomDescriptionUrl</x:v>
-      </x:c>
-      <x:c r="C24" s="385" t="str">
-        <x:v>조건부</x:v>
-      </x:c>
-      <x:c r="D24" s="385" t="str">
-        <x:v>""</x:v>
-      </x:c>
-      <x:c r="E24" s="385" t="str">
-        <x:v>하단 설명 링크</x:v>
-      </x:c>
-      <x:c r="F24" s="667" t="str"/>
-      <x:c r="G24" s="300"/>
-      <x:c r="H24" s="300"/>
-    </x:row>
-    <x:row r="25" ht="22" customHeight="1">
-      <x:c r="A25" s="695" t="str">
-        <x:v>showBottomDescription</x:v>
-      </x:c>
-      <x:c r="B25" s="668" t="str">
-        <x:v>popups[].content.showBottomDescription</x:v>
-      </x:c>
-      <x:c r="C25" s="668" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="D25" s="668" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="E25" s="668" t="str">
-        <x:v>하단 설명 표시</x:v>
-      </x:c>
-      <x:c r="F25" s="669" t="str"/>
-      <x:c r="G25" s="300"/>
-      <x:c r="H25" s="300"/>
-    </x:row>
-    <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="300"/>
-      <x:c r="B26" s="300"/>
-      <x:c r="C26" s="300"/>
-      <x:c r="D26" s="300"/>
-      <x:c r="E26" s="300"/>
-      <x:c r="F26" s="300"/>
-      <x:c r="G26" s="300"/>
-      <x:c r="H26" s="300"/>
-    </x:row>
-    <x:row r="27" ht="22" customHeight="1">
-      <x:c r="A27" s="678" t="str">
+      <x:c r="A24" s="678" t="str">
         <x:v>동작 메모
 • textBlocks가 있으면 서식 본문을 표시하고 없으면 plainText fallback.
 • MarkdownMode / MarkdownContent는 삭제된 기능.
+• contentTitle / description / showContentHeader는 삭제(설계 37). 콘텐츠 제목·설명은 textBlocks 앞 문단으로 작성하며 plainText 첫 줄에도 포함된다.
 • 공통 Overlay/Position/Font/Footer 옵션은 popups[] 최상위에서 받음.</x:v>
       </x:c>
-      <x:c r="B27" s="679"/>
-      <x:c r="C27" s="679"/>
-      <x:c r="D27" s="679"/>
-      <x:c r="E27" s="679"/>
-      <x:c r="F27" s="680"/>
+      <x:c r="B24" s="679"/>
+      <x:c r="C24" s="679"/>
+      <x:c r="D24" s="679"/>
+      <x:c r="E24" s="679"/>
+      <x:c r="F24" s="680"/>
+      <x:c r="G24" s="300"/>
+      <x:c r="H24" s="300"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="734"/>
+      <x:c r="B25" s="723"/>
+      <x:c r="C25" s="723"/>
+      <x:c r="D25" s="723"/>
+      <x:c r="E25" s="723"/>
+      <x:c r="F25" s="724"/>
+      <x:c r="G25" s="300"/>
+      <x:c r="H25" s="300"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="734"/>
+      <x:c r="B26" s="723"/>
+      <x:c r="C26" s="723"/>
+      <x:c r="D26" s="723"/>
+      <x:c r="E26" s="723"/>
+      <x:c r="F26" s="724"/>
+      <x:c r="G26" s="300"/>
+      <x:c r="H26" s="300"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="681"/>
+      <x:c r="B27" s="682"/>
+      <x:c r="C27" s="682"/>
+      <x:c r="D27" s="682"/>
+      <x:c r="E27" s="682"/>
+      <x:c r="F27" s="683"/>
       <x:c r="G27" s="300"/>
       <x:c r="H27" s="300"/>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="734"/>
-      <x:c r="B28" s="723"/>
-      <x:c r="C28" s="723"/>
-      <x:c r="D28" s="723"/>
-      <x:c r="E28" s="723"/>
-      <x:c r="F28" s="724"/>
+      <x:c r="A28" s="300"/>
+      <x:c r="B28" s="300"/>
+      <x:c r="C28" s="300"/>
+      <x:c r="D28" s="300"/>
+      <x:c r="E28" s="300"/>
+      <x:c r="F28" s="300"/>
       <x:c r="G28" s="300"/>
       <x:c r="H28" s="300"/>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
-      <x:c r="A29" s="734"/>
-      <x:c r="B29" s="723"/>
-      <x:c r="C29" s="723"/>
-      <x:c r="D29" s="723"/>
-      <x:c r="E29" s="723"/>
-      <x:c r="F29" s="724"/>
+      <x:c r="A29" s="300"/>
+      <x:c r="B29" s="300"/>
+      <x:c r="C29" s="300"/>
+      <x:c r="D29" s="300"/>
+      <x:c r="E29" s="300"/>
+      <x:c r="F29" s="300"/>
       <x:c r="G29" s="300"/>
       <x:c r="H29" s="300"/>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="681"/>
-      <x:c r="B30" s="682"/>
-      <x:c r="C30" s="682"/>
-      <x:c r="D30" s="682"/>
-      <x:c r="E30" s="682"/>
-      <x:c r="F30" s="683"/>
+      <x:c r="A30" s="300"/>
+      <x:c r="B30" s="300"/>
+      <x:c r="C30" s="300"/>
+      <x:c r="D30" s="300"/>
+      <x:c r="E30" s="300"/>
+      <x:c r="F30" s="300"/>
       <x:c r="G30" s="300"/>
       <x:c r="H30" s="300"/>
     </x:row>
@@ -7784,36 +7755,9 @@
       <x:c r="G157" s="300"/>
       <x:c r="H157" s="300"/>
     </x:row>
-    <x:row r="158" ht="22" customHeight="1">
-      <x:c r="A158" s="300"/>
-      <x:c r="B158" s="300"/>
-      <x:c r="C158" s="300"/>
-      <x:c r="D158" s="300"/>
-      <x:c r="E158" s="300"/>
-      <x:c r="F158" s="300"/>
-      <x:c r="G158" s="300"/>
-      <x:c r="H158" s="300"/>
-    </x:row>
-    <x:row r="159" ht="22" customHeight="1">
-      <x:c r="A159" s="300"/>
-      <x:c r="B159" s="300"/>
-      <x:c r="C159" s="300"/>
-      <x:c r="D159" s="300"/>
-      <x:c r="E159" s="300"/>
-      <x:c r="F159" s="300"/>
-      <x:c r="G159" s="300"/>
-      <x:c r="H159" s="300"/>
-    </x:row>
-    <x:row r="160" ht="22" customHeight="1">
-      <x:c r="A160" s="300"/>
-      <x:c r="B160" s="300"/>
-      <x:c r="C160" s="300"/>
-      <x:c r="D160" s="300"/>
-      <x:c r="E160" s="300"/>
-      <x:c r="F160" s="300"/>
-      <x:c r="G160" s="300"/>
-      <x:c r="H160" s="300"/>
-    </x:row>
+    <x:row r="158" ht="22" customHeight="1"/>
+    <x:row r="159" ht="22" customHeight="1"/>
+    <x:row r="160" ht="22" customHeight="1"/>
     <x:row r="161" ht="22" customHeight="1"/>
     <x:row r="162" ht="22" customHeight="1"/>
     <x:row r="163" ht="22" customHeight="1"/>
@@ -7831,14 +7775,11 @@
     <x:row r="175" ht="22" customHeight="1"/>
     <x:row r="176" ht="22" customHeight="1"/>
     <x:row r="177" ht="22" customHeight="1"/>
-    <x:row r="178" ht="22" customHeight="1"/>
-    <x:row r="179" ht="22" customHeight="1"/>
-    <x:row r="180" ht="22" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="3">
     <x:mergeCell ref="A1:F2"/>
     <x:mergeCell ref="A4:F4"/>
-    <x:mergeCell ref="A27:F30"/>
+    <x:mergeCell ref="A24:F27"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -13547,10 +13488,8 @@
   "showDoNotShowAgain": false,
   "questions": [],
   "content": {
-    "plainText": "서비스 점검이 진행됩니다.",
-    "showPlainText": true,
-    "contentTitle": "점검 공지",
-    "showContentHeader": true
+    "plainText": "점검 공지\n서비스 점검이 진행됩니다.",
+    "showPlainText": true
   }
 }</x:v>
       </x:c>

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -3162,7 +3162,7 @@
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="661" t="str">
-        <x:v>WPF 결과 일괄 API</x:v>
+        <x:v>WPF 결과 수신 API(1건)</x:v>
       </x:c>
       <x:c r="B10" s="662" t="str">
         <x:v>→</x:v>
@@ -3188,7 +3188,7 @@
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="678" t="str">
-        <x:v>상세 흐름: 관리자 화면 → 관리자 API → Oracle → WPF 전용 목록 API → PopupResponseDto → PopupFactory → PopupOptions + 타입별 View → PopupManager → PopupWindow → 사용자 동작 → 로컬 pending-results 저장 → WPF 결과 일괄 API → Oracle</x:v>
+        <x:v>상세 흐름: 관리자 화면 → 관리자 API → Oracle → WPF 전용 조회 API(1건, deliveryId) → PopupResponseDto → PopupFactory → PopupOptions + 타입별 View → PopupManager → PopupWindow → 사용자 동작 → 로컬 pending-results 저장 → WPF 결과 수신 API(1건) → Oracle → nextStatus(AVAILABLE: 즉시 다음 조회 / EMPTY: 조회 간격 대기)</x:v>
       </x:c>
       <x:c r="B12" s="679"/>
       <x:c r="C12" s="679"/>
@@ -3388,7 +3388,7 @@
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
       <x:c r="A26" s="648" t="str">
-        <x:v>③ WPF 목록 API 응답 ROOT</x:v>
+        <x:v>③ WPF 조회 API 응답 ROOT (POST /api/wpf/popups, 설계 35)</x:v>
       </x:c>
       <x:c r="B26" s="648"/>
       <x:c r="C26" s="648"/>
@@ -3431,13 +3431,13 @@
         <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B29" s="693" t="str">
-        <x:v>serverTime</x:v>
+        <x:v>popup</x:v>
       </x:c>
       <x:c r="C29" s="693" t="str">
-        <x:v>서버 기준 시각</x:v>
+        <x:v>표시할 팝업 1건 또는 null</x:v>
       </x:c>
       <x:c r="D29" s="696" t="str">
-        <x:v>진단용. 표시/조회주기 판단에는 사용하지 않음</x:v>
+        <x:v>null이면 pollingIntervalSeconds 뒤 다시 조회</x:v>
       </x:c>
       <x:c r="E29" s="171"/>
       <x:c r="F29" s="172"/>
@@ -3446,16 +3446,16 @@
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" s="666" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>popup</x:v>
       </x:c>
       <x:c r="B30" s="385" t="str">
-        <x:v>userId</x:v>
+        <x:v>deliveryId</x:v>
       </x:c>
       <x:c r="C30" s="385" t="str">
-        <x:v>인증 정보에서 확인한 사용자 ID</x:v>
+        <x:v>서버 발급 전달 건 ID</x:v>
       </x:c>
       <x:c r="D30" s="667" t="str">
-        <x:v>진단용. 요청에는 userId 없음</x:v>
+        <x:v>결과 수신 시 그대로 반환. 응답 유실 후 재조회는 같은 값</x:v>
       </x:c>
       <x:c r="E30" s="171"/>
       <x:c r="F30" s="172"/>
@@ -3482,16 +3482,16 @@
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" s="695" t="str">
-        <x:v>ROOT</x:v>
+        <x:v>(삭제)</x:v>
       </x:c>
       <x:c r="B32" s="668" t="str">
-        <x:v>popups[]</x:v>
+        <x:v>serverTime / userId / popups[]</x:v>
       </x:c>
       <x:c r="C32" s="668" t="str">
-        <x:v>서버가 최종 판정한 표시 대상 목록</x:v>
+        <x:v>설계 35 단건 조회로 삭제</x:v>
       </x:c>
       <x:c r="D32" s="669" t="str">
-        <x:v>WPF는 기간/대상 재판정하지 않음</x:v>
+        <x:v>nextStatus는 결과 응답에만 있음</x:v>
       </x:c>
       <x:c r="E32" s="171"/>
       <x:c r="F32" s="172"/>
@@ -3531,22 +3531,22 @@
       <x:c r="H35" s="173"/>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
-      <x:c r="A36" s="678" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">• displayStartAt / displayEndAt 및 period/repeat 계열은 WPF 목록 응답에서 제거.
+      <x:c r="A36" s="678" t="str">
+        <x:v>• displayStartAt / displayEndAt 및 period/repeat 계열은 WPF 목록 응답에서 제거.
 • IMAGE content.linkUrl(이미지 클릭 시 URL 열기) 삭제. 모든 이미지 모드에서 클릭 동작 없음.
 • footerAction / footerLinkUrl은 content가 아니라 popups[] 최상위.
 • useBackgroundOverlay / backgroundOverlayOpacity / popupPosition / headerFontSize / bodyFontSize / footerFontSize도 popups[] 최상위.
 • showCloseButton legacy 수신 제거, showFooterButton만 사용.
 • VIDEO content.allowSeek 추가(기본 true). VIDEO+QUIZ에도 동일 적용.
 • RESULT Request의 responseStartedAt 제거.
-• RESULT Response는 results[] + resultId/popupId/resultType/status/code/message만 유지.
+• RESULT Response는 결과 1건의 resultId/status/nextStatus/code/message만 유지(설계 35에서 results[]·popupId·resultType 삭제).
 • status는 ACCEPTED / DUPLICATE / REJECTED / RETRYABLE_ERROR / INTERNAL_ERROR.
 • totalScore/passed/hiddenUntil/watchedRatio/requiredRatio/receivedAt/popupStatus/completed/completedAt/responseId는 Response에서 제거.
 • 설문·퀴즈 footerAction은 SUBMIT만 허용(CLOSE·LINK_AND_CLOSE 명시는 관리자 저장 거부).
-• 항목 검증 오류는 그 항목만 REJECTED(WPF_INVALID_RESULT), 검증 후 변환 예외는 INTERNAL_ERROR(WPF_INTERNAL). 요청 외곽·JSON 역직렬화 오류만 HTTP 400.
-• WPF 큐는 ACCEPTED·DUPLICATE·REJECTED만 삭제, 그 밖의 상태·응답 누락·요청 실패는 보관 후 같은 resultId로 재전송.</x:t>
-        </x:is>
+• 항목 검증 오류는 그 항목만 REJECTED(WPF_INVALID_RESULT), 검증 후 변환 예외는 INTERNAL_ERROR(WPF_INTERNAL). JSON 역직렬화 오류만 HTTP 400.
+• WPF 큐는 ACCEPTED·DUPLICATE·REJECTED만 삭제, 그 밖의 상태·응답 누락·요청 실패는 보관 후 같은 resultId로 재전송.
+• [설계 35] 조회는 POST 단건(popup + deliveryId), 결과는 1건씩 순서대로 전송. 미종결 결과가 남으면 다음 조회를 미룸(장애 복구 정책 확정 전 임시 기준).
+• [설계 35] TEXT·IMAGE 닫기(CLOSE·LINK_AND_CLOSE)는 완료 처리. 설문·퀴즈·영상 미완료 결과는 저장 시각부터 pollingIntervalSeconds 동안 재노출 유예.</x:v>
       </x:c>
       <x:c r="B36" s="679"/>
       <x:c r="C36" s="679"/>
@@ -3980,7 +3980,7 @@
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="648" t="str">
-        <x:v>popups[] 공통 응답 필드</x:v>
+        <x:v>popup 공통 응답 필드 (설계 35: 조회 응답 popup 객체 1건, 대상이 없으면 popup=null)</x:v>
       </x:c>
       <x:c r="B4" s="648"/>
       <x:c r="C4" s="648"/>
@@ -4017,7 +4017,7 @@
         <x:v>popupId</x:v>
       </x:c>
       <x:c r="B6" s="693" t="str">
-        <x:v>popups[].popupId</x:v>
+        <x:v>popup.popupId</x:v>
       </x:c>
       <x:c r="C6" s="693" t="str">
         <x:v>Y</x:v>
@@ -4039,7 +4039,7 @@
         <x:v>popupType</x:v>
       </x:c>
       <x:c r="B7" s="385" t="str">
-        <x:v>popups[].popupType</x:v>
+        <x:v>popup.popupType</x:v>
       </x:c>
       <x:c r="C7" s="385" t="str">
         <x:v>Y</x:v>
@@ -4061,7 +4061,7 @@
         <x:v>title</x:v>
       </x:c>
       <x:c r="B8" s="385" t="str">
-        <x:v>popups[].title</x:v>
+        <x:v>popup.title</x:v>
       </x:c>
       <x:c r="C8" s="385" t="str">
         <x:v>Y(계약)</x:v>
@@ -4081,7 +4081,7 @@
         <x:v>displayMode</x:v>
       </x:c>
       <x:c r="B9" s="385" t="str">
-        <x:v>popups[].displayMode</x:v>
+        <x:v>popup.displayMode</x:v>
       </x:c>
       <x:c r="C9" s="385" t="str">
         <x:v>Y(계약)</x:v>
@@ -4098,22 +4098,22 @@
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="666" t="str">
-        <x:v>displayOrder</x:v>
+        <x:v>deliveryId</x:v>
       </x:c>
       <x:c r="B10" s="385" t="str">
-        <x:v>popups[].displayOrder</x:v>
+        <x:v>popup.deliveryId</x:v>
       </x:c>
       <x:c r="C10" s="385" t="str">
-        <x:v>Y(계약)</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="D10" s="385" t="str">
-        <x:v>100</x:v>
+        <x:v>없음</x:v>
       </x:c>
       <x:c r="E10" s="385" t="str">
-        <x:v>작은 값 우선</x:v>
+        <x:v>서버 발급 전달 건 ID</x:v>
       </x:c>
       <x:c r="F10" s="667" t="str">
-        <x:v>같은 값은 같은 표시 그룹</x:v>
+        <x:v>결과 수신 요청에 그대로 반환. displayOrder는 서버 정렬 전용이라 응답에서 삭제(설계 35)</x:v>
       </x:c>
       <x:c r="G10" s="300"/>
       <x:c r="H10" s="300"/>
@@ -4123,7 +4123,7 @@
         <x:v>sizeMode</x:v>
       </x:c>
       <x:c r="B11" s="385" t="str">
-        <x:v>popups[].sizeMode</x:v>
+        <x:v>popup.sizeMode</x:v>
       </x:c>
       <x:c r="C11" s="385" t="str">
         <x:v>Y(계약)</x:v>
@@ -4143,7 +4143,7 @@
         <x:v>width</x:v>
       </x:c>
       <x:c r="B12" s="385" t="str">
-        <x:v>popups[].width</x:v>
+        <x:v>popup.width</x:v>
       </x:c>
       <x:c r="C12" s="385" t="str">
         <x:v>조건부</x:v>
@@ -4165,7 +4165,7 @@
         <x:v>height</x:v>
       </x:c>
       <x:c r="B13" s="385" t="str">
-        <x:v>popups[].height</x:v>
+        <x:v>popup.height</x:v>
       </x:c>
       <x:c r="C13" s="385" t="str">
         <x:v>조건부</x:v>
@@ -4187,7 +4187,7 @@
         <x:v>widthRatio</x:v>
       </x:c>
       <x:c r="B14" s="385" t="str">
-        <x:v>popups[].widthRatio</x:v>
+        <x:v>popup.widthRatio</x:v>
       </x:c>
       <x:c r="C14" s="385" t="str">
         <x:v>RATIO</x:v>
@@ -4207,7 +4207,7 @@
         <x:v>heightRatio</x:v>
       </x:c>
       <x:c r="B15" s="385" t="str">
-        <x:v>popups[].heightRatio</x:v>
+        <x:v>popup.heightRatio</x:v>
       </x:c>
       <x:c r="C15" s="385" t="str">
         <x:v>RATIO</x:v>
@@ -4227,7 +4227,7 @@
         <x:v>minimumWidth</x:v>
       </x:c>
       <x:c r="B16" s="385" t="str">
-        <x:v>popups[].minimumWidth</x:v>
+        <x:v>popup.minimumWidth</x:v>
       </x:c>
       <x:c r="C16" s="385" t="str">
         <x:v>N</x:v>
@@ -4247,7 +4247,7 @@
         <x:v>minimumHeight</x:v>
       </x:c>
       <x:c r="B17" s="385" t="str">
-        <x:v>popups[].minimumHeight</x:v>
+        <x:v>popup.minimumHeight</x:v>
       </x:c>
       <x:c r="C17" s="385" t="str">
         <x:v>N</x:v>
@@ -4267,7 +4267,7 @@
         <x:v>maximumWidth</x:v>
       </x:c>
       <x:c r="B18" s="385" t="str">
-        <x:v>popups[].maximumWidth</x:v>
+        <x:v>popup.maximumWidth</x:v>
       </x:c>
       <x:c r="C18" s="385" t="str">
         <x:v>N</x:v>
@@ -4289,7 +4289,7 @@
         <x:v>maximumHeight</x:v>
       </x:c>
       <x:c r="B19" s="385" t="str">
-        <x:v>popups[].maximumHeight</x:v>
+        <x:v>popup.maximumHeight</x:v>
       </x:c>
       <x:c r="C19" s="385" t="str">
         <x:v>N</x:v>
@@ -4311,7 +4311,7 @@
         <x:v>showHeader</x:v>
       </x:c>
       <x:c r="B20" s="385" t="str">
-        <x:v>popups[].showHeader</x:v>
+        <x:v>popup.showHeader</x:v>
       </x:c>
       <x:c r="C20" s="385" t="str">
         <x:v>Y(계약)</x:v>
@@ -4331,7 +4331,7 @@
         <x:v>showFooterButton</x:v>
       </x:c>
       <x:c r="B21" s="385" t="str">
-        <x:v>popups[].showFooterButton</x:v>
+        <x:v>popup.showFooterButton</x:v>
       </x:c>
       <x:c r="C21" s="385" t="str">
         <x:v>Y(계약)</x:v>
@@ -4353,7 +4353,7 @@
         <x:v>showFooter</x:v>
       </x:c>
       <x:c r="B22" s="385" t="str">
-        <x:v>popups[].showFooter</x:v>
+        <x:v>popup.showFooter</x:v>
       </x:c>
       <x:c r="C22" s="385" t="str">
         <x:v>Y(계약)</x:v>
@@ -4373,7 +4373,7 @@
         <x:v>footerAction</x:v>
       </x:c>
       <x:c r="B23" s="385" t="str">
-        <x:v>popups[].footerAction</x:v>
+        <x:v>popup.footerAction</x:v>
       </x:c>
       <x:c r="C23" s="385" t="str">
         <x:v>N</x:v>
@@ -4395,7 +4395,7 @@
         <x:v>footerLinkUrl</x:v>
       </x:c>
       <x:c r="B24" s="385" t="str">
-        <x:v>popups[].footerLinkUrl</x:v>
+        <x:v>popup.footerLinkUrl</x:v>
       </x:c>
       <x:c r="C24" s="385" t="str">
         <x:v>조건부</x:v>
@@ -4417,7 +4417,7 @@
         <x:v>useBackgroundOverlay</x:v>
       </x:c>
       <x:c r="B25" s="385" t="str">
-        <x:v>popups[].useBackgroundOverlay</x:v>
+        <x:v>popup.useBackgroundOverlay</x:v>
       </x:c>
       <x:c r="C25" s="385" t="str">
         <x:v>N</x:v>
@@ -4439,7 +4439,7 @@
         <x:v>backgroundOverlayOpacity</x:v>
       </x:c>
       <x:c r="B26" s="748" t="str">
-        <x:v>popups[].backgroundOverlayOpacity</x:v>
+        <x:v>popup.backgroundOverlayOpacity</x:v>
       </x:c>
       <x:c r="C26" s="748" t="str">
         <x:v>N</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>popupPosition</x:v>
       </x:c>
       <x:c r="B27" s="751" t="str">
-        <x:v>popups[].popupPosition</x:v>
+        <x:v>popup.popupPosition</x:v>
       </x:c>
       <x:c r="C27" s="751" t="str">
         <x:v>N</x:v>
@@ -4483,7 +4483,7 @@
         <x:v>headerFontSize</x:v>
       </x:c>
       <x:c r="B28" s="385" t="str">
-        <x:v>popups[].headerFontSize</x:v>
+        <x:v>popup.headerFontSize</x:v>
       </x:c>
       <x:c r="C28" s="385" t="str">
         <x:v>N</x:v>
@@ -4505,7 +4505,7 @@
         <x:v>bodyFontSize</x:v>
       </x:c>
       <x:c r="B29" s="385" t="str">
-        <x:v>popups[].bodyFontSize</x:v>
+        <x:v>popup.bodyFontSize</x:v>
       </x:c>
       <x:c r="C29" s="385" t="str">
         <x:v>N</x:v>
@@ -4527,7 +4527,7 @@
         <x:v>footerFontSize</x:v>
       </x:c>
       <x:c r="B30" s="385" t="str">
-        <x:v>popups[].footerFontSize</x:v>
+        <x:v>popup.footerFontSize</x:v>
       </x:c>
       <x:c r="C30" s="385" t="str">
         <x:v>N</x:v>
@@ -4549,7 +4549,7 @@
         <x:v>showDoNotShowAgain</x:v>
       </x:c>
       <x:c r="B31" s="385" t="str">
-        <x:v>popups[].showDoNotShowAgain</x:v>
+        <x:v>popup.showDoNotShowAgain</x:v>
       </x:c>
       <x:c r="C31" s="385" t="str">
         <x:v>Y(계약)</x:v>
@@ -4569,7 +4569,7 @@
         <x:v>hideDays</x:v>
       </x:c>
       <x:c r="B32" s="385" t="str">
-        <x:v>popups[].hideDays</x:v>
+        <x:v>popup.hideDays</x:v>
       </x:c>
       <x:c r="C32" s="385" t="str">
         <x:v>N</x:v>
@@ -4591,7 +4591,7 @@
         <x:v>completionRatio</x:v>
       </x:c>
       <x:c r="B33" s="385" t="str">
-        <x:v>popups[].completionRatio</x:v>
+        <x:v>popup.completionRatio</x:v>
       </x:c>
       <x:c r="C33" s="385" t="str">
         <x:v>VIDEO/VIDEO+QUIZ</x:v>
@@ -4613,7 +4613,7 @@
         <x:v>allowCloseBeforeComplete</x:v>
       </x:c>
       <x:c r="B34" s="385" t="str">
-        <x:v>popups[].allowCloseBeforeComplete</x:v>
+        <x:v>popup.allowCloseBeforeComplete</x:v>
       </x:c>
       <x:c r="C34" s="385" t="str">
         <x:v>VIDEO/VIDEO+QUIZ</x:v>
@@ -4635,7 +4635,7 @@
         <x:v>passingScore</x:v>
       </x:c>
       <x:c r="B35" s="385" t="str">
-        <x:v>popups[].passingScore</x:v>
+        <x:v>popup.passingScore</x:v>
       </x:c>
       <x:c r="C35" s="385" t="str">
         <x:v>Y(QUIZ)</x:v>
@@ -4657,7 +4657,7 @@
         <x:v>questions[]</x:v>
       </x:c>
       <x:c r="B36" s="385" t="str">
-        <x:v>popups[].questions[]</x:v>
+        <x:v>popup.questions[]</x:v>
       </x:c>
       <x:c r="C36" s="385" t="str">
         <x:v>Y(SURVEY/QUIZ)</x:v>
@@ -4677,7 +4677,7 @@
         <x:v>content</x:v>
       </x:c>
       <x:c r="B37" s="757" t="str">
-        <x:v>popups[].content</x:v>
+        <x:v>popup.content</x:v>
       </x:c>
       <x:c r="C37" s="757" t="str">
         <x:v>Y</x:v>
@@ -6042,7 +6042,7 @@
         <x:v>plainText</x:v>
       </x:c>
       <x:c r="B6" s="693" t="str">
-        <x:v>popups[].content.plainText</x:v>
+        <x:v>popup.content.plainText</x:v>
       </x:c>
       <x:c r="C6" s="693" t="str">
         <x:v>조건부</x:v>
@@ -6064,7 +6064,7 @@
         <x:v>textBlocks</x:v>
       </x:c>
       <x:c r="B7" s="385" t="str">
-        <x:v>popups[].content.textBlocks[]</x:v>
+        <x:v>popup.content.textBlocks[]</x:v>
       </x:c>
       <x:c r="C7" s="385" t="str">
         <x:v>조건부</x:v>
@@ -6086,7 +6086,7 @@
         <x:v>textBlocks[].alignment</x:v>
       </x:c>
       <x:c r="B8" s="385" t="str">
-        <x:v>popups[].content.textBlocks[].alignment</x:v>
+        <x:v>popup.content.textBlocks[].alignment</x:v>
       </x:c>
       <x:c r="C8" s="385" t="str">
         <x:v>N</x:v>
@@ -6110,7 +6110,7 @@
         <x:v>textBlocks[].runs[]</x:v>
       </x:c>
       <x:c r="B9" s="385" t="str">
-        <x:v>popups[].content.textBlocks[].runs[]</x:v>
+        <x:v>popup.content.textBlocks[].runs[]</x:v>
       </x:c>
       <x:c r="C9" s="385" t="str">
         <x:v>Y(textBlocks)</x:v>
@@ -6282,7 +6282,7 @@
         <x:v>showPlainText</x:v>
       </x:c>
       <x:c r="B17" s="772" t="str">
-        <x:v>popups[].content.showPlainText</x:v>
+        <x:v>popup.content.showPlainText</x:v>
       </x:c>
       <x:c r="C17" s="772" t="str">
         <x:v>N</x:v>
@@ -6302,7 +6302,7 @@
         <x:v>highlightText</x:v>
       </x:c>
       <x:c r="B18" s="385" t="str">
-        <x:v>popups[].content.highlightText</x:v>
+        <x:v>popup.content.highlightText</x:v>
       </x:c>
       <x:c r="C18" s="385" t="str">
         <x:v>N</x:v>
@@ -6322,7 +6322,7 @@
         <x:v>showHighlight</x:v>
       </x:c>
       <x:c r="B19" s="385" t="str">
-        <x:v>popups[].content.showHighlight</x:v>
+        <x:v>popup.content.showHighlight</x:v>
       </x:c>
       <x:c r="C19" s="385" t="str">
         <x:v>N</x:v>
@@ -6344,7 +6344,7 @@
         <x:v>bottomDescription</x:v>
       </x:c>
       <x:c r="B20" s="385" t="str">
-        <x:v>popups[].content.bottomDescription</x:v>
+        <x:v>popup.content.bottomDescription</x:v>
       </x:c>
       <x:c r="C20" s="385" t="str">
         <x:v>N</x:v>
@@ -6364,7 +6364,7 @@
         <x:v>bottomDescriptionUrl</x:v>
       </x:c>
       <x:c r="B21" s="385" t="str">
-        <x:v>popups[].content.bottomDescriptionUrl</x:v>
+        <x:v>popup.content.bottomDescriptionUrl</x:v>
       </x:c>
       <x:c r="C21" s="385" t="str">
         <x:v>조건부</x:v>
@@ -6384,7 +6384,7 @@
         <x:v>showBottomDescription</x:v>
       </x:c>
       <x:c r="B22" s="668" t="str">
-        <x:v>popups[].content.showBottomDescription</x:v>
+        <x:v>popup.content.showBottomDescription</x:v>
       </x:c>
       <x:c r="C22" s="668" t="str">
         <x:v>N</x:v>
@@ -7868,7 +7868,7 @@
         <x:v>imageUrl</x:v>
       </x:c>
       <x:c r="B6" s="693" t="str">
-        <x:v>popups[].content.imageUrl</x:v>
+        <x:v>popup.content.imageUrl</x:v>
       </x:c>
       <x:c r="C6" s="693" t="str">
         <x:v>Y</x:v>
@@ -7890,7 +7890,7 @@
         <x:v>imageSizeMode</x:v>
       </x:c>
       <x:c r="B7" s="385" t="str">
-        <x:v>popups[].content.imageSizeMode</x:v>
+        <x:v>popup.content.imageSizeMode</x:v>
       </x:c>
       <x:c r="C7" s="385" t="str">
         <x:v>N</x:v>
@@ -7910,7 +7910,7 @@
         <x:v>imageTitle</x:v>
       </x:c>
       <x:c r="B8" s="385" t="str">
-        <x:v>popups[].content.imageTitle</x:v>
+        <x:v>popup.content.imageTitle</x:v>
       </x:c>
       <x:c r="C8" s="385" t="str">
         <x:v>N</x:v>
@@ -7932,7 +7932,7 @@
         <x:v>description</x:v>
       </x:c>
       <x:c r="B9" s="385" t="str">
-        <x:v>popups[].content.description</x:v>
+        <x:v>popup.content.description</x:v>
       </x:c>
       <x:c r="C9" s="385" t="str">
         <x:v>N</x:v>
@@ -7952,7 +7952,7 @@
         <x:v>showDescription</x:v>
       </x:c>
       <x:c r="B10" s="385" t="str">
-        <x:v>popups[].content.showDescription</x:v>
+        <x:v>popup.content.showDescription</x:v>
       </x:c>
       <x:c r="C10" s="385" t="str">
         <x:v>N</x:v>
@@ -7972,7 +7972,7 @@
         <x:v>width</x:v>
       </x:c>
       <x:c r="B11" s="385" t="str">
-        <x:v>popups[].content.width</x:v>
+        <x:v>popup.content.width</x:v>
       </x:c>
       <x:c r="C11" s="385" t="str">
         <x:v>N</x:v>
@@ -7994,7 +7994,7 @@
         <x:v>height</x:v>
       </x:c>
       <x:c r="B12" s="385" t="str">
-        <x:v>popups[].content.height</x:v>
+        <x:v>popup.content.height</x:v>
       </x:c>
       <x:c r="C12" s="385" t="str">
         <x:v>N</x:v>
@@ -8016,7 +8016,7 @@
         <x:v>keepAspectRatio</x:v>
       </x:c>
       <x:c r="B13" s="668" t="str">
-        <x:v>popups[].content.keepAspectRatio</x:v>
+        <x:v>popup.content.keepAspectRatio</x:v>
       </x:c>
       <x:c r="C13" s="668" t="str">
         <x:v>N</x:v>
@@ -9623,7 +9623,7 @@
         <x:v>videoUrl</x:v>
       </x:c>
       <x:c r="B6" s="693" t="str">
-        <x:v>popups[].content.videoUrl</x:v>
+        <x:v>popup.content.videoUrl</x:v>
       </x:c>
       <x:c r="C6" s="693" t="str">
         <x:v>Y</x:v>
@@ -9643,7 +9643,7 @@
         <x:v>videoTitle</x:v>
       </x:c>
       <x:c r="B7" s="385" t="str">
-        <x:v>popups[].content.videoTitle</x:v>
+        <x:v>popup.content.videoTitle</x:v>
       </x:c>
       <x:c r="C7" s="385" t="str">
         <x:v>N</x:v>
@@ -9663,7 +9663,7 @@
         <x:v>description</x:v>
       </x:c>
       <x:c r="B8" s="385" t="str">
-        <x:v>popups[].content.description</x:v>
+        <x:v>popup.content.description</x:v>
       </x:c>
       <x:c r="C8" s="385" t="str">
         <x:v>N</x:v>
@@ -9683,7 +9683,7 @@
         <x:v>showDescription</x:v>
       </x:c>
       <x:c r="B9" s="385" t="str">
-        <x:v>popups[].content.showDescription</x:v>
+        <x:v>popup.content.showDescription</x:v>
       </x:c>
       <x:c r="C9" s="385" t="str">
         <x:v>N</x:v>
@@ -9703,7 +9703,7 @@
         <x:v>showControls</x:v>
       </x:c>
       <x:c r="B10" s="385" t="str">
-        <x:v>popups[].content.showControls</x:v>
+        <x:v>popup.content.showControls</x:v>
       </x:c>
       <x:c r="C10" s="385" t="str">
         <x:v>N</x:v>
@@ -9723,7 +9723,7 @@
         <x:v>allowFullScreen</x:v>
       </x:c>
       <x:c r="B11" s="385" t="str">
-        <x:v>popups[].content.allowFullScreen</x:v>
+        <x:v>popup.content.allowFullScreen</x:v>
       </x:c>
       <x:c r="C11" s="385" t="str">
         <x:v>N</x:v>
@@ -9745,7 +9745,7 @@
         <x:v>allowPlaybackRateChange</x:v>
       </x:c>
       <x:c r="B12" s="385" t="str">
-        <x:v>popups[].content.allowPlaybackRateChange</x:v>
+        <x:v>popup.content.allowPlaybackRateChange</x:v>
       </x:c>
       <x:c r="C12" s="385" t="str">
         <x:v>N</x:v>
@@ -9767,7 +9767,7 @@
         <x:v>allowSeek</x:v>
       </x:c>
       <x:c r="B13" s="385" t="str">
-        <x:v>popups[].content.allowSeek</x:v>
+        <x:v>popup.content.allowSeek</x:v>
       </x:c>
       <x:c r="C13" s="385" t="str">
         <x:v>N</x:v>
@@ -9789,7 +9789,7 @@
         <x:v>autoPlay</x:v>
       </x:c>
       <x:c r="B14" s="385" t="str">
-        <x:v>popups[].content.autoPlay</x:v>
+        <x:v>popup.content.autoPlay</x:v>
       </x:c>
       <x:c r="C14" s="385" t="str">
         <x:v>N</x:v>
@@ -9809,7 +9809,7 @@
         <x:v>isLoop</x:v>
       </x:c>
       <x:c r="B15" s="385" t="str">
-        <x:v>popups[].content.isLoop</x:v>
+        <x:v>popup.content.isLoop</x:v>
       </x:c>
       <x:c r="C15" s="385" t="str">
         <x:v>N</x:v>
@@ -9829,7 +9829,7 @@
         <x:v>defaultVolume</x:v>
       </x:c>
       <x:c r="B16" s="385" t="str">
-        <x:v>popups[].content.defaultVolume</x:v>
+        <x:v>popup.content.defaultVolume</x:v>
       </x:c>
       <x:c r="C16" s="385" t="str">
         <x:v>N</x:v>
@@ -9851,7 +9851,7 @@
         <x:v>completionRatio</x:v>
       </x:c>
       <x:c r="B17" s="385" t="str">
-        <x:v>popups[].completionRatio</x:v>
+        <x:v>popup.completionRatio</x:v>
       </x:c>
       <x:c r="C17" s="385" t="str">
         <x:v>VIDEO/VIDEO+QUIZ</x:v>
@@ -9873,7 +9873,7 @@
         <x:v>allowCloseBeforeComplete</x:v>
       </x:c>
       <x:c r="B18" s="668" t="str">
-        <x:v>popups[].allowCloseBeforeComplete</x:v>
+        <x:v>popup.allowCloseBeforeComplete</x:v>
       </x:c>
       <x:c r="C18" s="668" t="str">
         <x:v>VIDEO/VIDEO+QUIZ</x:v>
@@ -11434,7 +11434,7 @@
         <x:v>questions[]</x:v>
       </x:c>
       <x:c r="B6" s="693" t="str">
-        <x:v>popups[].questions[]</x:v>
+        <x:v>popup.questions[]</x:v>
       </x:c>
       <x:c r="C6" s="693" t="str">
         <x:v>Y</x:v>
@@ -11458,7 +11458,7 @@
         <x:v>questionId</x:v>
       </x:c>
       <x:c r="B7" s="385" t="str">
-        <x:v>popups[].questions[].questionId</x:v>
+        <x:v>popup.questions[].questionId</x:v>
       </x:c>
       <x:c r="C7" s="385" t="str">
         <x:v>Y</x:v>
@@ -11482,7 +11482,7 @@
         <x:v>title</x:v>
       </x:c>
       <x:c r="B8" s="385" t="str">
-        <x:v>popups[].questions[].title</x:v>
+        <x:v>popup.questions[].title</x:v>
       </x:c>
       <x:c r="C8" s="385" t="str">
         <x:v>Y</x:v>
@@ -11506,7 +11506,7 @@
         <x:v>description</x:v>
       </x:c>
       <x:c r="B9" s="385" t="str">
-        <x:v>popups[].questions[].description</x:v>
+        <x:v>popup.questions[].description</x:v>
       </x:c>
       <x:c r="C9" s="385" t="str">
         <x:v>N</x:v>
@@ -11528,7 +11528,7 @@
         <x:v>questionType</x:v>
       </x:c>
       <x:c r="B10" s="385" t="str">
-        <x:v>popups[].questions[].questionType</x:v>
+        <x:v>popup.questions[].questionType</x:v>
       </x:c>
       <x:c r="C10" s="385" t="str">
         <x:v>Y</x:v>
@@ -11550,7 +11550,7 @@
         <x:v>isRequired</x:v>
       </x:c>
       <x:c r="B11" s="385" t="str">
-        <x:v>popups[].questions[].isRequired</x:v>
+        <x:v>popup.questions[].isRequired</x:v>
       </x:c>
       <x:c r="C11" s="385" t="str">
         <x:v>N</x:v>
@@ -11574,7 +11574,7 @@
         <x:v>optionLayout</x:v>
       </x:c>
       <x:c r="B12" s="385" t="str">
-        <x:v>popups[].questions[].optionLayout</x:v>
+        <x:v>popup.questions[].optionLayout</x:v>
       </x:c>
       <x:c r="C12" s="385" t="str">
         <x:v>N</x:v>
@@ -11596,7 +11596,7 @@
         <x:v>isScored</x:v>
       </x:c>
       <x:c r="B13" s="385" t="str">
-        <x:v>popups[].questions[].isScored</x:v>
+        <x:v>popup.questions[].isScored</x:v>
       </x:c>
       <x:c r="C13" s="385" t="str">
         <x:v>false</x:v>
@@ -11620,7 +11620,7 @@
         <x:v>questionScore</x:v>
       </x:c>
       <x:c r="B14" s="385" t="str">
-        <x:v>popups[].questions[].questionScore</x:v>
+        <x:v>popup.questions[].questionScore</x:v>
       </x:c>
       <x:c r="C14" s="385" t="str">
         <x:v>-</x:v>
@@ -11644,7 +11644,7 @@
         <x:v>correctAnswer</x:v>
       </x:c>
       <x:c r="B15" s="385" t="str">
-        <x:v>popups[].questions[].correctAnswer</x:v>
+        <x:v>popup.questions[].correctAnswer</x:v>
       </x:c>
       <x:c r="C15" s="385" t="str">
         <x:v>-</x:v>
@@ -11666,7 +11666,7 @@
         <x:v>answerMatchMode</x:v>
       </x:c>
       <x:c r="B16" s="385" t="str">
-        <x:v>popups[].questions[].answerMatchMode</x:v>
+        <x:v>popup.questions[].answerMatchMode</x:v>
       </x:c>
       <x:c r="C16" s="385" t="str">
         <x:v>-</x:v>
@@ -11688,7 +11688,7 @@
         <x:v>options[]</x:v>
       </x:c>
       <x:c r="B17" s="385" t="str">
-        <x:v>popups[].questions[].options[]</x:v>
+        <x:v>popup.questions[].options[]</x:v>
       </x:c>
       <x:c r="C17" s="385" t="str">
         <x:v>조건부</x:v>
@@ -11712,7 +11712,7 @@
         <x:v>optionId</x:v>
       </x:c>
       <x:c r="B18" s="385" t="str">
-        <x:v>popups[].questions[].options[].optionId</x:v>
+        <x:v>popup.questions[].options[].optionId</x:v>
       </x:c>
       <x:c r="C18" s="385" t="str">
         <x:v>Y(선택형)</x:v>
@@ -11736,7 +11736,7 @@
         <x:v>value</x:v>
       </x:c>
       <x:c r="B19" s="385" t="str">
-        <x:v>popups[].questions[].options[].value</x:v>
+        <x:v>popup.questions[].options[].value</x:v>
       </x:c>
       <x:c r="C19" s="385" t="str">
         <x:v>N</x:v>
@@ -11760,7 +11760,7 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B20" s="385" t="str">
-        <x:v>popups[].questions[].options[].text</x:v>
+        <x:v>popup.questions[].options[].text</x:v>
       </x:c>
       <x:c r="C20" s="385" t="str">
         <x:v>Y(선택형)</x:v>
@@ -11782,7 +11782,7 @@
         <x:v>isCorrect</x:v>
       </x:c>
       <x:c r="B21" s="385" t="str">
-        <x:v>popups[].questions[].options[].isCorrect</x:v>
+        <x:v>popup.questions[].options[].isCorrect</x:v>
       </x:c>
       <x:c r="C21" s="385" t="str">
         <x:v>-</x:v>
@@ -11806,7 +11806,7 @@
         <x:v>passingScore</x:v>
       </x:c>
       <x:c r="B22" s="668" t="str">
-        <x:v>popups[].passingScore</x:v>
+        <x:v>popup.passingScore</x:v>
       </x:c>
       <x:c r="C22" s="668" t="str">
         <x:v>-</x:v>
@@ -11876,7 +11876,7 @@
         <x:v>videoEnabled</x:v>
       </x:c>
       <x:c r="B26" s="793" t="str">
-        <x:v>popups[].content.videoEnabled</x:v>
+        <x:v>popup.content.videoEnabled</x:v>
       </x:c>
       <x:c r="C26" s="793" t="str">
         <x:v>N</x:v>
@@ -11900,7 +11900,7 @@
         <x:v>videoUrl</x:v>
       </x:c>
       <x:c r="B27" s="772" t="str">
-        <x:v>popups[].content.videoUrl</x:v>
+        <x:v>popup.content.videoUrl</x:v>
       </x:c>
       <x:c r="C27" s="772" t="str">
         <x:v>-</x:v>
@@ -11924,7 +11924,7 @@
         <x:v>videoTitle</x:v>
       </x:c>
       <x:c r="B28" s="772" t="str">
-        <x:v>popups[].content.videoTitle</x:v>
+        <x:v>popup.content.videoTitle</x:v>
       </x:c>
       <x:c r="C28" s="772" t="str">
         <x:v>-</x:v>
@@ -11946,7 +11946,7 @@
         <x:v>showControls</x:v>
       </x:c>
       <x:c r="B29" s="772" t="str">
-        <x:v>popups[].content.showControls</x:v>
+        <x:v>popup.content.showControls</x:v>
       </x:c>
       <x:c r="C29" s="772" t="str">
         <x:v>-</x:v>
@@ -11968,7 +11968,7 @@
         <x:v>allowFullScreen</x:v>
       </x:c>
       <x:c r="B30" s="772" t="str">
-        <x:v>popups[].content.allowFullScreen</x:v>
+        <x:v>popup.content.allowFullScreen</x:v>
       </x:c>
       <x:c r="C30" s="772" t="str">
         <x:v>-</x:v>
@@ -11990,7 +11990,7 @@
         <x:v>allowPlaybackRateChange</x:v>
       </x:c>
       <x:c r="B31" s="772" t="str">
-        <x:v>popups[].content.allowPlaybackRateChange</x:v>
+        <x:v>popup.content.allowPlaybackRateChange</x:v>
       </x:c>
       <x:c r="C31" s="772" t="str">
         <x:v>-</x:v>
@@ -12012,7 +12012,7 @@
         <x:v>allowSeek</x:v>
       </x:c>
       <x:c r="B32" s="385" t="str">
-        <x:v>popups[].content.allowSeek</x:v>
+        <x:v>popup.content.allowSeek</x:v>
       </x:c>
       <x:c r="C32" s="385" t="str">
         <x:v>-</x:v>
@@ -12036,7 +12036,7 @@
         <x:v>autoPlay</x:v>
       </x:c>
       <x:c r="B33" s="748" t="str">
-        <x:v>popups[].content.autoPlay</x:v>
+        <x:v>popup.content.autoPlay</x:v>
       </x:c>
       <x:c r="C33" s="748" t="str">
         <x:v>-</x:v>
@@ -12058,7 +12058,7 @@
         <x:v>isLoop</x:v>
       </x:c>
       <x:c r="B34" s="772" t="str">
-        <x:v>popups[].content.isLoop</x:v>
+        <x:v>popup.content.isLoop</x:v>
       </x:c>
       <x:c r="C34" s="772" t="str">
         <x:v>-</x:v>
@@ -12080,7 +12080,7 @@
         <x:v>defaultVolume</x:v>
       </x:c>
       <x:c r="B35" s="772" t="str">
-        <x:v>popups[].content.defaultVolume</x:v>
+        <x:v>popup.content.defaultVolume</x:v>
       </x:c>
       <x:c r="C35" s="772" t="str">
         <x:v>-</x:v>
@@ -12102,7 +12102,7 @@
         <x:v>completionRatio</x:v>
       </x:c>
       <x:c r="B36" s="772" t="str">
-        <x:v>popups[].completionRatio</x:v>
+        <x:v>popup.completionRatio</x:v>
       </x:c>
       <x:c r="C36" s="772" t="str">
         <x:v>-</x:v>
@@ -12126,7 +12126,7 @@
         <x:v>allowCloseBeforeComplete</x:v>
       </x:c>
       <x:c r="B37" s="757" t="str">
-        <x:v>popups[].allowCloseBeforeComplete</x:v>
+        <x:v>popup.allowCloseBeforeComplete</x:v>
       </x:c>
       <x:c r="C37" s="757" t="str">
         <x:v>-</x:v>
@@ -13470,11 +13470,11 @@
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="833" t="str">
         <x:v>{
+  "deliveryId": "DLV-0001",
   "popupId": "TEXT-001",
   "popupType": "TEXT",
   "title": "서비스 안내",
   "displayMode": "SEQUENTIAL",
-  "displayOrder": 100,
   "sizeMode": "FIXED",
   "width": 900,
   "height": 620,
@@ -15108,7 +15108,7 @@
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="795" t="str">
-        <x:v>WPF 결과 API 요청 - POST /api/wpf/popups/results</x:v>
+        <x:v>WPF 결과 API 요청 - POST /api/wpf/popups/results (결과 1건, 설계 35)</x:v>
       </x:c>
       <x:c r="B1" s="795"/>
       <x:c r="C1" s="795"/>
@@ -15166,7 +15166,7 @@
         <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B6" s="693" t="str">
-        <x:v>clientRequestId</x:v>
+        <x:v>(본문)</x:v>
       </x:c>
       <x:c r="C6" s="693" t="str">
         <x:v>전체</x:v>
@@ -15175,10 +15175,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E6" s="693" t="str">
-        <x:v>없음</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="F6" s="693" t="str">
-        <x:v>전송 요청 단위 GUID</x:v>
+        <x:v>결과 객체 1건(배열 아님). 이전 clientRequestId·sentAt·results[] 일괄 구조는 삭제</x:v>
       </x:c>
       <x:c r="G6" s="696" t="str">
         <x:v>서버 요청 로그 진단용, resultId와 역할 다름</x:v>
@@ -15189,21 +15189,19 @@
         <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B7" s="385" t="str">
-        <x:v>sentAt</x:v>
+        <x:v>deliveryId</x:v>
       </x:c>
       <x:c r="C7" s="385" t="str">
         <x:v>전체</x:v>
       </x:c>
-      <x:c r="D7" s="385" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">N(서버) / WPF 항상 전송</x:t>
-        </x:is>
+      <x:c r="D7" s="385" t="str">
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="E7" s="385" t="str">
-        <x:v>현재 전송 시각</x:v>
+        <x:v>없음</x:v>
       </x:c>
       <x:c r="F7" s="385" t="str">
-        <x:v>HTTP 전송 시각</x:v>
+        <x:v>조회 응답 popup.deliveryId 그대로. 서버가 소유·팝업 일치·미종료 검증</x:v>
       </x:c>
       <x:c r="G7" s="667" t="inlineStr">
         <x:is>
@@ -15216,19 +15214,19 @@
         <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B8" s="385" t="str">
-        <x:v>results[]</x:v>
+        <x:v>(재전송)</x:v>
       </x:c>
       <x:c r="C8" s="385" t="str">
         <x:v>전체</x:v>
       </x:c>
       <x:c r="D8" s="385" t="str">
-        <x:v>Y</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="E8" s="385" t="str">
-        <x:v>[]</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="F8" s="385" t="str">
-        <x:v>결과 항목 배열</x:v>
+        <x:v>같은 결과는 resultId·deliveryId·본문을 바꾸지 않고 다시 보냄</x:v>
       </x:c>
       <x:c r="G8" s="667" t="str">
         <x:v>1~50개</x:v>
@@ -15236,7 +15234,7 @@
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B9" s="385" t="str">
         <x:v>resultId</x:v>
@@ -15259,7 +15257,7 @@
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B10" s="385" t="str">
         <x:v>popupId</x:v>
@@ -15280,7 +15278,7 @@
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B11" s="385" t="str">
         <x:v>resultType</x:v>
@@ -15303,7 +15301,7 @@
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B12" s="385" t="str">
         <x:v>displayedAt</x:v>
@@ -15324,7 +15322,7 @@
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B13" s="385" t="str">
         <x:v>closedAt</x:v>
@@ -15347,7 +15345,7 @@
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B14" s="385" t="str">
         <x:v>hideDays</x:v>
@@ -15370,7 +15368,7 @@
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B15" s="385" t="str">
         <x:v>answers[]</x:v>
@@ -15395,7 +15393,7 @@
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" s="666" t="str">
-        <x:v>results[].answers[]</x:v>
+        <x:v>answers[]</x:v>
       </x:c>
       <x:c r="B16" s="385" t="str">
         <x:v>questionId</x:v>
@@ -15416,7 +15414,7 @@
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
       <x:c r="A17" s="666" t="str">
-        <x:v>results[].answers[]</x:v>
+        <x:v>answers[]</x:v>
       </x:c>
       <x:c r="B17" s="385" t="str">
         <x:v>optionIds[]</x:v>
@@ -15441,7 +15439,7 @@
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
       <x:c r="A18" s="666" t="str">
-        <x:v>results[].answers[]</x:v>
+        <x:v>answers[]</x:v>
       </x:c>
       <x:c r="B18" s="385" t="str">
         <x:v>textAnswer</x:v>
@@ -15464,7 +15462,7 @@
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
       <x:c r="A19" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B19" s="385" t="str">
         <x:v>score</x:v>
@@ -15487,7 +15485,7 @@
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B20" s="385" t="str">
         <x:v>passed</x:v>
@@ -15510,7 +15508,7 @@
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B21" s="385" t="str">
         <x:v>video</x:v>
@@ -15533,7 +15531,7 @@
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
       <x:c r="A22" s="666" t="str">
-        <x:v>results[].video</x:v>
+        <x:v>video</x:v>
       </x:c>
       <x:c r="B22" s="385" t="str">
         <x:v>durationSeconds</x:v>
@@ -15554,7 +15552,7 @@
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
       <x:c r="A23" s="666" t="str">
-        <x:v>results[].video</x:v>
+        <x:v>video</x:v>
       </x:c>
       <x:c r="B23" s="385" t="str">
         <x:v>positionSeconds</x:v>
@@ -15575,7 +15573,7 @@
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
       <x:c r="A24" s="666" t="str">
-        <x:v>results[].video</x:v>
+        <x:v>video</x:v>
       </x:c>
       <x:c r="B24" s="385" t="str">
         <x:v>maximumPositionSeconds</x:v>
@@ -15596,7 +15594,7 @@
     </x:row>
     <x:row r="25" ht="22" customHeight="1">
       <x:c r="A25" s="695" t="str">
-        <x:v>results[].video</x:v>
+        <x:v>video</x:v>
       </x:c>
       <x:c r="B25" s="668" t="str">
         <x:v>watchedSeconds</x:v>
@@ -15638,16 +15636,15 @@
       <x:c r="G27" s="796"/>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="821" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CLOSED: 일반 종료
+      <x:c r="A28" s="821" t="str">
+        <x:v>CLOSED: 일반 종료
 HIDDEN: 다시 보지 않기 선택
 SUBMITTED: SURVEY / QUIZ / VIDEO+QUIZ 정상 제출
 VIDEO_WATCHED: 단독 VIDEO 종료 또는 VIDEO+QUIZ를 제출하지 않고 종료한 경우 영상 시청 결과
 ※ 우선순위: 다시 보지 않기를 선택하면 영상 시청 기록이 있어도 HIDDEN
 ※ responseStartedAt은 삭제됨. displayedAt과 동일값이어서 중복이었음.
-※ 결과는 먼저 로컬 pending-results에 저장하고, 통신 실패 시 같은 resultId로 재전송.</x:t>
-        </x:is>
+※ 결과는 먼저 로컬 pending-results에 저장하고, 저장된 순서대로 1건씩 전송. 통신 실패 시 같은 resultId로 재전송.
+※ [설계 35] TEXT·IMAGE의 CLOSED(Footer 닫기·바로가기 포함)는 완료로 저장. 설문·퀴즈·영상이 미완료로 끝나면 조회 간격 동안 재노출 유예.</x:v>
       </x:c>
       <x:c r="B28" s="822"/>
       <x:c r="C28" s="822"/>
@@ -15716,28 +15713,29 @@
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="833" t="str">
         <x:v>{
-  "clientRequestId": "REQ-001",
-  "sentAt": "2026-10-12T16:20:00+09:00",
-  "results": [
+  "resultId": "RESULT-001",
+  "deliveryId": "DLV-0001",
+  "popupId": "VIDEO-QUIZ-001",
+  "resultType": "SUBMITTED",
+  "displayedAt": "2026-10-12T16:10:00+09:00",
+  "closedAt": "2026-10-12T16:20:00+09:00",
+  "answers": [
     {
-      "resultId": "RESULT-001",
-      "popupId": "VIDEO-QUIZ-001",
-      "resultType": "SUBMITTED",
-      "displayedAt": "2026-10-12T16:10:00+09:00",
-      "closedAt": "2026-10-12T16:20:00+09:00",
-      "answers": [
-        { "questionId": 301, "optionIds": [3001], "textAnswer": null }
+      "questionId": 301,
+      "optionIds": [
+        3001
       ],
-      "score": 100,
-      "passed": true,
-      "video": {
-        "durationSeconds": 600,
-        "positionSeconds": 590,
-        "maximumPositionSeconds": 600,
-        "watchedSeconds": 540
-      }
+      "textAnswer": null
     }
-  ]
+  ],
+  "score": 100,
+  "passed": true,
+  "video": {
+    "durationSeconds": 600,
+    "positionSeconds": 590,
+    "maximumPositionSeconds": 600,
+    "watchedSeconds": 540
+  }
 }</x:v>
       </x:c>
       <x:c r="B36" s="834"/>
@@ -16031,7 +16029,7 @@
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="795" t="str">
-        <x:v>WPF 결과 API 응답 - POST /api/wpf/popups/results</x:v>
+        <x:v>WPF 결과 API 응답 - POST /api/wpf/popups/results (결과 1건, 설계 35)</x:v>
       </x:c>
       <x:c r="B1" s="795"/>
       <x:c r="C1" s="795"/>
@@ -16089,7 +16087,7 @@
         <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B6" s="693" t="str">
-        <x:v>results[]</x:v>
+        <x:v>resultId</x:v>
       </x:c>
       <x:c r="C6" s="693" t="str">
         <x:v>전체</x:v>
@@ -16098,10 +16096,10 @@
         <x:v>Y</x:v>
       </x:c>
       <x:c r="E6" s="693" t="str">
-        <x:v>[]</x:v>
+        <x:v>없음</x:v>
       </x:c>
       <x:c r="F6" s="693" t="str">
-        <x:v>항목별 처리 결과</x:v>
+        <x:v>요청 resultId echo</x:v>
       </x:c>
       <x:c r="G6" s="696" t="str">
         <x:v>응답은 요청 항목 순서 유지</x:v>
@@ -16109,10 +16107,10 @@
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B7" s="385" t="str">
-        <x:v>resultId</x:v>
+        <x:v>status</x:v>
       </x:c>
       <x:c r="C7" s="385" t="str">
         <x:v>전체</x:v>
@@ -16124,7 +16122,7 @@
         <x:v>없음</x:v>
       </x:c>
       <x:c r="F7" s="385" t="str">
-        <x:v>요청 resultId echo</x:v>
+        <x:v>저장 처리 상태</x:v>
       </x:c>
       <x:c r="G7" s="667" t="str">
         <x:v>WPF 큐 대응 키</x:v>
@@ -16132,22 +16130,22 @@
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B8" s="385" t="str">
-        <x:v>popupId</x:v>
+        <x:v>nextStatus</x:v>
       </x:c>
       <x:c r="C8" s="385" t="str">
-        <x:v>전체</x:v>
+        <x:v>ACCEPTED·DUPLICATE</x:v>
       </x:c>
       <x:c r="D8" s="385" t="str">
-        <x:v>Y</x:v>
+        <x:v>조건부</x:v>
       </x:c>
       <x:c r="E8" s="385" t="str">
-        <x:v>없음</x:v>
+        <x:v>null</x:v>
       </x:c>
       <x:c r="F8" s="385" t="str">
-        <x:v>요청 popupId echo</x:v>
+        <x:v>후속 후보 유무 AVAILABLE / EMPTY. 후보 확인 실패면 생략(EMPTY로 바꾸지 않음)</x:v>
       </x:c>
       <x:c r="G8" s="667" t="str">
         <x:v>거절/미종결 진단 로그용</x:v>
@@ -16155,22 +16153,22 @@
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B9" s="385" t="str">
-        <x:v>resultType</x:v>
+        <x:v>code</x:v>
       </x:c>
       <x:c r="C9" s="385" t="str">
-        <x:v>전체</x:v>
+        <x:v>오류</x:v>
       </x:c>
       <x:c r="D9" s="385" t="str">
-        <x:v>Y</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="E9" s="385" t="str">
-        <x:v>없음</x:v>
+        <x:v>null</x:v>
       </x:c>
       <x:c r="F9" s="385" t="str">
-        <x:v>요청 resultType echo</x:v>
+        <x:v>오류/거절 사유 코드. 설계 35 추가: WPF_INVALID_DELIVERY·WPF_DELIVERY_COMPLETED·WPF_NEXT_STATUS_UNKNOWN</x:v>
       </x:c>
       <x:c r="G9" s="667" t="str">
         <x:v>진단 로그용</x:v>
@@ -16178,22 +16176,22 @@
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>ROOT</x:v>
       </x:c>
       <x:c r="B10" s="385" t="str">
-        <x:v>status</x:v>
+        <x:v>message</x:v>
       </x:c>
       <x:c r="C10" s="385" t="str">
-        <x:v>전체</x:v>
+        <x:v>오류</x:v>
       </x:c>
       <x:c r="D10" s="385" t="str">
-        <x:v>Y</x:v>
+        <x:v>N</x:v>
       </x:c>
       <x:c r="E10" s="385" t="str">
-        <x:v>없음</x:v>
+        <x:v>null</x:v>
       </x:c>
       <x:c r="F10" s="385" t="str">
-        <x:v>처리 상태</x:v>
+        <x:v>오류/거절 설명</x:v>
       </x:c>
       <x:c r="G10" s="667" t="str">
         <x:v>ACCEPTED / DUPLICATE / REJECTED / RETRYABLE_ERROR / INTERNAL_ERROR</x:v>
@@ -16201,22 +16199,22 @@
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="666" t="str">
-        <x:v>results[]</x:v>
+        <x:v>(삭제)</x:v>
       </x:c>
       <x:c r="B11" s="385" t="str">
-        <x:v>code</x:v>
+        <x:v>results[] / popupId / resultType</x:v>
       </x:c>
       <x:c r="C11" s="385" t="str">
-        <x:v>오류</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="D11" s="385" t="str">
-        <x:v>N</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="E11" s="385" t="str">
-        <x:v>null</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="F11" s="385" t="str">
-        <x:v>오류/거절 사유 코드</x:v>
+        <x:v>설계 35 단건 응답으로 삭제</x:v>
       </x:c>
       <x:c r="G11" s="667" t="str">
         <x:v>예: WPF_INVALID_RESULT / WPF_RETRYABLE / WPF_INTERNAL</x:v>
@@ -16224,22 +16222,22 @@
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="695" t="str">
-        <x:v>results[]</x:v>
+        <x:v>nextStatus 처리</x:v>
       </x:c>
       <x:c r="B12" s="668" t="str">
-        <x:v>message</x:v>
+        <x:v>AVAILABLE → 즉시 조회</x:v>
       </x:c>
       <x:c r="C12" s="668" t="str">
-        <x:v>오류</x:v>
+        <x:v>EMPTY → 대기</x:v>
       </x:c>
       <x:c r="D12" s="668" t="str">
-        <x:v>N</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="E12" s="668" t="str">
-        <x:v>null</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="F12" s="668" t="str">
-        <x:v>오류/거절 설명</x:v>
+        <x:v>EMPTY는 최신 pollingIntervalSeconds 대기. 생략이면 즉시 조회(popup=null 정상 처리)</x:v>
       </x:c>
       <x:c r="G12" s="669" t="str">
         <x:v>내부 오류 상세는 노출하지 않음</x:v>
@@ -16390,6 +16388,7 @@
     <x:row r="23" ht="22" customHeight="1">
       <x:c r="A23" s="678" t="str">
         <x:v>receivedAt / popupStatus / completed / completedAt / responseId / totalScore / passed / hiddenUntil / watchedRatio / requiredRatio
+results[] / popupId / resultType (설계 35 단건 응답)
 → WPF가 사용하지 않거나 요청 값과 중복되어 Response에서 제거.
 → 서버 내부 DB 저장·숨김 만료·시청 기록·완료 판정·로깅 자체는 유지.</x:v>
       </x:c>
@@ -16457,27 +16456,18 @@
       <x:c r="G29" s="862"/>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="833" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{
-  "results": [
-    {
-      "resultId": "RESULT-001",
-      "popupId": "VIDEO-QUIZ-001",
-      "resultType": "SUBMITTED",
-      "status": "ACCEPTED"
-    },
-    {
-      "resultId": "RESULT-002",
-      "popupId": "VIDEO-002",
-      "resultType": "VIDEO_WATCHED",
-      "status": "RETRYABLE_ERROR",
-      "code": "WPF_RETRYABLE",
-      "message": "일시적인 서버 오류로 처리하지 못했습니다. 다시 전송해 주세요."
-    }
-  ]
-}</x:t>
-        </x:is>
+      <x:c r="A30" s="833" t="str">
+        <x:v>{
+  "resultId": "RESULT-001",
+  "status": "ACCEPTED",
+  "nextStatus": "AVAILABLE"
+}
+{
+  "resultId": "RESULT-002",
+  "status": "RETRYABLE_ERROR",
+  "code": "WPF_RETRYABLE",
+  "message": "일시적인 서버 오류로 처리하지 못했습니다. 다시 전송해 주세요."
+}</x:v>
       </x:c>
       <x:c r="B30" s="834"/>
       <x:c r="C30" s="834"/>
@@ -16662,10 +16652,8 @@
       </x:c>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">
-      <x:c r="A46" s="669" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">역직렬화 후 항목 검증 오류(resultId·popupId 누락, 알 수 없는 resultType, hideDays 범위, score 음수, answers·optionIds null 요소, video 형식)</x:t>
-        </x:is>
+      <x:c r="A46" s="669" t="str">
+        <x:v>역직렬화 후 항목 검증 오류(resultId·deliveryId·popupId 누락, 알 수 없는 resultType, hideDays 범위, score 음수, answers·optionIds null 요소, video 형식)</x:v>
       </x:c>
       <x:c r="B46" s="669" t="inlineStr">
         <x:is>
@@ -16682,10 +16670,8 @@
           <x:t xml:space="preserve">WPF_INVALID_RESULT</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46" s="669" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">사유 기록 후 삭제. 같은 요청의 다른 항목은 정상 처리</x:t>
-        </x:is>
+      <x:c r="E46" s="669" t="str">
+        <x:v>사유 기록 후 삭제. 다음 결과 전송·조회는 계속</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
@@ -16743,10 +16729,8 @@
       </x:c>
     </x:row>
     <x:row r="49" ht="48" customHeight="1">
-      <x:c r="A49" s="669" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">요청 외곽 구조(clientRequestId, results 1~50개)·JSON 역직렬화 오류(잘못된 날짜·숫자 자료형 등)</x:t>
-        </x:is>
+      <x:c r="A49" s="669" t="str">
+        <x:v>JSON 역직렬화 오류(잘못된 날짜·숫자 자료형·배열 본문 등)</x:v>
       </x:c>
       <x:c r="B49" s="669" t="inlineStr">
         <x:is>
@@ -16763,10 +16747,8 @@
           <x:t xml:space="preserve">WPF_BAD_REQUEST</x:t>
         </x:is>
       </x:c>
-      <x:c r="E49" s="669" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">전송한 결과 보관. batch를 나눠 다시 보내고 단독으로도 400인 항목만 이번 실행에서 제외(파일 보관)</x:t>
-        </x:is>
+      <x:c r="E49" s="669" t="str">
+        <x:v>이 결과만 이번 실행에서 제외(파일 보관). 다음 결과 전송은 계속</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="48" customHeight="1">
@@ -16790,10 +16772,8 @@
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="E50" s="669" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">전송한 결과 모두 보관·재전송</x:t>
-        </x:is>
+      <x:c r="E50" s="669" t="str">
+        <x:v>보관하고 다음 조회를 미룬 뒤 복구 간격으로 같은 resultId 재전송(설계 35 임시 기준)</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="34" customHeight="1">

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -3036,7 +3036,7 @@
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="647" t="str">
-        <x:v>WPF 팝업 인터페이스 개요 (main 최신 반영)</x:v>
+        <x:v>WPF 팝업 인터페이스 개요 (계약 v3.7 · 2026-10-13 · 설계 35·37·39·46 반영)</x:v>
       </x:c>
       <x:c r="B1" s="647"/>
       <x:c r="C1" s="647"/>
@@ -3108,7 +3108,7 @@
         <x:v>→</x:v>
       </x:c>
       <x:c r="G6" s="652" t="str">
-        <x:v>WPF 목록 API</x:v>
+        <x:v>WPF 조회 API(1건)</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str"/>
     </x:row>
@@ -3532,10 +3532,10 @@
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="678" t="str">
-        <x:v>• displayStartAt / displayEndAt 및 period/repeat 계열은 WPF 목록 응답에서 제거.
+        <x:v>• displayStartAt / displayEndAt 및 period/repeat 계열은 WPF 조회 응답에서 제거.
 • IMAGE content.linkUrl(이미지 클릭 시 URL 열기) 삭제. 모든 이미지 모드에서 클릭 동작 없음.
-• footerAction / footerLinkUrl은 content가 아니라 popups[] 최상위.
-• useBackgroundOverlay / backgroundOverlayOpacity / popupPosition / headerFontSize / bodyFontSize / footerFontSize도 popups[] 최상위.
+• footerAction / footerLinkUrl은 content가 아니라 popup 최상위.
+• useBackgroundOverlay / backgroundOverlayOpacity / popupPosition / headerFontSize / bodyFontSize / footerFontSize도 popup 최상위.
 • showCloseButton legacy 수신 제거, showFooterButton만 사용.
 • VIDEO content.allowSeek 추가(기본 true). VIDEO+QUIZ에도 동일 적용.
 • RESULT Request의 responseStartedAt 제거.
@@ -4578,10 +4578,10 @@
         <x:v>null → HIDDEN 시 30일</x:v>
       </x:c>
       <x:c r="E32" s="385" t="str">
-        <x:v>숨김 일수</x:v>
+        <x:v>숨김 일수(1~3650)</x:v>
       </x:c>
       <x:c r="F32" s="667" t="str">
-        <x:v>Result HIDDEN의 hideDays 생성에 사용</x:v>
+        <x:v>Result HIDDEN의 hideDays 생성에 사용. 관리자 저장도 1~3650만 허용(설계 46)</x:v>
       </x:c>
       <x:c r="G32" s="300"/>
       <x:c r="H32" s="300"/>
@@ -6415,6 +6415,8 @@
 • textBlocks가 있으면 서식 본문을 표시하고 없으면 plainText fallback.
 • MarkdownMode / MarkdownContent는 삭제된 기능.
 • contentTitle / description / showContentHeader는 삭제(설계 37). 콘텐츠 제목·설명은 textBlocks 앞 문단으로 작성하며 plainText 첫 줄에도 포함된다.
+• 통합 전 행은 조회 시 제목(LEFT·굵게·24)→설명→본문 순으로 합친다. showContentHeader=false였던 행은 합치지 않는다.
+• 헤더 표시·본문 숨김(showPlainText=false)이던 행은 헤더만 보이기: 제목·설명 문단만 보내고 숨긴 본문은 빼며 showPlainText=true(설계 39). 관리자 재저장 시 숨긴 본문 삭제.
 • 공통 Overlay/Position/Font/Footer 옵션은 popups[] 최상위에서 받음.</x:v>
       </x:c>
       <x:c r="B24" s="679"/>
@@ -13775,6 +13777,7 @@
     <x:row r="34" ht="22" customHeight="1">
       <x:c r="A34" s="833" t="str">
         <x:v>{
+  "deliveryId": "DLV-0002",
   "popupId": "IMAGE-001",
   "popupType": "IMAGE",
   "title": "교육 안내",
@@ -14014,6 +14017,7 @@
     <x:row r="56" ht="22" customHeight="1">
       <x:c r="A56" s="833" t="str">
         <x:v>{
+  "deliveryId": "DLV-0003",
   "popupId": "VIDEO-001",
   "popupType": "VIDEO",
   "title": "보안 교육",
@@ -14262,6 +14266,7 @@
     <x:row r="79" ht="22" customHeight="1">
       <x:c r="A79" s="833" t="str">
         <x:v>{
+  "deliveryId": "DLV-0004",
   "popupId": "SURVEY-001",
   "popupType": "SURVEY",
   "title": "교육 만족도 설문",
@@ -14275,8 +14280,16 @@
       "isScored": false,
       "optionLayout": "VERTICAL",
       "options": [
-        {"optionId": 1001, "value": "YES", "text": "네"},
-        {"optionId": 1002, "value": "NO", "text": "아니요"}
+        {
+          "optionId": 1001,
+          "value": "YES",
+          "text": "네"
+        },
+        {
+          "optionId": 1002,
+          "value": "NO",
+          "text": "아니요"
+        }
       ]
     },
     {
@@ -14546,6 +14559,7 @@
     <x:row r="110" ht="22" customHeight="1">
       <x:c r="A110" s="833" t="str">
         <x:v>{
+  "deliveryId": "DLV-0005",
   "popupId": "QUIZ-001",
   "popupType": "QUIZ",
   "title": "보안 확인 퀴즈",
@@ -14561,8 +14575,18 @@
       "questionScore": 100,
       "optionLayout": "VERTICAL",
       "options": [
-        {"optionId": 2001, "value": "HTTPS", "text": "HTTPS", "isCorrect": true},
-        {"optionId": 2002, "value": "HTTP", "text": "HTTP", "isCorrect": false}
+        {
+          "optionId": 2001,
+          "value": "HTTPS",
+          "text": "HTTPS",
+          "isCorrect": true
+        },
+        {
+          "optionId": 2002,
+          "value": "HTTP",
+          "text": "HTTP",
+          "isCorrect": false
+        }
       ]
     }
   ],
@@ -14801,6 +14825,7 @@
     <x:row r="140" ht="22" customHeight="1">
       <x:c r="A140" s="833" t="str">
         <x:v>{
+  "deliveryId": "DLV-0006",
   "popupId": "VIDEO-QUIZ-001",
   "popupType": "QUIZ",
   "title": "영상 교육 및 확인 퀴즈",
@@ -14817,15 +14842,25 @@
       "isScored": true,
       "questionScore": 100,
       "options": [
-        {"optionId": 3001, "value": "HTTPS", "text": "HTTPS", "isCorrect": true},
-        {"optionId": 3002, "value": "HTTP", "text": "HTTP", "isCorrect": false}
+        {
+          "optionId": 3001,
+          "value": "HTTPS",
+          "text": "HTTPS",
+          "isCorrect": true
+        },
+        {
+          "optionId": 3002,
+          "value": "HTTP",
+          "text": "HTTP",
+          "isCorrect": false
+        }
       ]
     }
   ],
   "content": {
     "videoEnabled": true,
     "videoUrl": "https://example.com/media/security.mp4",
-    "videoTitle": "교육 영상",
+    "videoTitle": "영상 확인 퀴즈",
     "surveyTitle": "영상 확인 퀴즈",
     "showControls": true,
     "allowFullScreen": true,
@@ -15181,7 +15216,7 @@
         <x:v>결과 객체 1건(배열 아님). 이전 clientRequestId·sentAt·results[] 일괄 구조는 삭제</x:v>
       </x:c>
       <x:c r="G6" s="696" t="str">
-        <x:v>서버 요청 로그 진단용, resultId와 역할 다름</x:v>
+        <x:v>이전 envelope(clientRequestId·sentAt·results[]) 없음</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -15203,10 +15238,8 @@
       <x:c r="F7" s="385" t="str">
         <x:v>조회 응답 popup.deliveryId 그대로. 서버가 소유·팝업 일치·미종료 검증</x:v>
       </x:c>
-      <x:c r="G7" s="667" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">서버 업무 로직 미사용·필수 검증 없음</x:t>
-        </x:is>
+      <x:c r="G7" s="667" t="str">
+        <x:v>서버가 존재·소유 사번·팝업 일치·미종료를 검증(WPF_INVALID_DELIVERY / WPF_DELIVERY_COMPLETED)</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
@@ -15229,7 +15262,7 @@
         <x:v>같은 결과는 resultId·deliveryId·본문을 바꾸지 않고 다시 보냄</x:v>
       </x:c>
       <x:c r="G8" s="667" t="str">
-        <x:v>1~50개</x:v>
+        <x:v>resultId·deliveryId·본문 유지</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
@@ -16102,7 +16135,7 @@
         <x:v>요청 resultId echo</x:v>
       </x:c>
       <x:c r="G6" s="696" t="str">
-        <x:v>응답은 요청 항목 순서 유지</x:v>
+        <x:v>요청 resultId와 같음</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -16125,7 +16158,7 @@
         <x:v>저장 처리 상태</x:v>
       </x:c>
       <x:c r="G7" s="667" t="str">
-        <x:v>WPF 큐 대응 키</x:v>
+        <x:v>WPF 큐 대응 키: ACCEPTED / DUPLICATE / REJECTED / RETRYABLE_ERROR / INTERNAL_ERROR</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
@@ -16148,7 +16181,7 @@
         <x:v>후속 후보 유무 AVAILABLE / EMPTY. 후보 확인 실패면 생략(EMPTY로 바꾸지 않음)</x:v>
       </x:c>
       <x:c r="G8" s="667" t="str">
-        <x:v>거절/미종결 진단 로그용</x:v>
+        <x:v>거절·실패에는 없음. WPF는 AVAILABLE·생략이면 즉시 조회, EMPTY면 대기</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
@@ -16171,7 +16204,7 @@
         <x:v>오류/거절 사유 코드. 설계 35 추가: WPF_INVALID_DELIVERY·WPF_DELIVERY_COMPLETED·WPF_NEXT_STATUS_UNKNOWN</x:v>
       </x:c>
       <x:c r="G9" s="667" t="str">
-        <x:v>진단 로그용</x:v>
+        <x:v>예: WPF_INVALID_RESULT / WPF_INVALID_DELIVERY / WPF_DELIVERY_COMPLETED / WPF_RETRYABLE / WPF_INTERNAL / WPF_NEXT_STATUS_UNKNOWN</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
@@ -16194,7 +16227,7 @@
         <x:v>오류/거절 설명</x:v>
       </x:c>
       <x:c r="G10" s="667" t="str">
-        <x:v>ACCEPTED / DUPLICATE / REJECTED / RETRYABLE_ERROR / INTERNAL_ERROR</x:v>
+        <x:v>내부 오류 상세는 노출하지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
@@ -16217,7 +16250,7 @@
         <x:v>설계 35 단건 응답으로 삭제</x:v>
       </x:c>
       <x:c r="G11" s="667" t="str">
-        <x:v>예: WPF_INVALID_RESULT / WPF_RETRYABLE / WPF_INTERNAL</x:v>
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
@@ -16240,7 +16273,7 @@
         <x:v>EMPTY는 최신 pollingIntervalSeconds 대기. 생략이면 즉시 조회(popup=null 정상 처리)</x:v>
       </x:c>
       <x:c r="G12" s="669" t="str">
-        <x:v>내부 오류 상세는 노출하지 않음</x:v>
+        <x:v/>
       </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -10927,7 +10927,7 @@
 • 로컬 영상은 MediaElement, HTTP/HTTPS 직접 영상은 WebView2 HTML5 video.
 • 두 경로 모두 공통 WPF Overlay 컨트롤바 사용, Chromium 기본 controls는 사용하지 않음.
 • allowSeek=false면 seek만 차단하고 진행률/시간 표시는 유지.
-• 시청 완료 판단은 watchedSeconds / durationSeconds 기준이며 탐색한 구간은 watchedSeconds에 합산하지 않음.
+• 시청 완료 판단은 min(watchedSeconds, durationSeconds) / durationSeconds를 소수점 4자리에서 내린 비율 기준이며(서버·VIDEO+QUIZ 동일, 설계 53-16) 탐색한 구간은 watchedSeconds에 합산하지 않음.
 • completionRatio / allowCloseBeforeComplete는 content가 아니라 popup 최상위.
 • YouTube iframe 지원은 제거됨.</t>
         </is>
@@ -13563,7 +13563,8 @@
 • 선택형 QUIZ는 선택 optionId 집합과 isCorrect=true 집합이 정확히 같을 때 정답, 부분 점수 없음.
 • TEXT QUIZ는 correctAnswer + EXACT/CONTAINS 사용 가능.
 • WPF가 score/passed를 최종 판정하고 통과한 QUIZ만 SUBMITTED 전송.
-• VIDEO+QUIZ는 watchedSeconds / durationSeconds가 completionRatio 이상일 때 퀴즈 입력/제출 활성화.
+• VIDEO+QUIZ는 watchedSeconds / durationSeconds(소수점 4자리 내림)가 completionRatio 이상일 때 퀴즈 입력/제출 활성화.
+• VIDEO+QUIZ는 영상 영역에 보인 제목·설명과 같은 퀴즈 머리말을 반복 표시하지 않음(설계 53-16).
 • VIDEO+SURVEY 계약은 없음.</t>
         </is>
       </c>

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -3794,7 +3794,8 @@
 • 항목 검증 오류는 그 항목만 REJECTED(WPF_INVALID_RESULT), 검증 후 변환 예외는 INTERNAL_ERROR(WPF_INTERNAL). JSON 역직렬화 오류만 HTTP 400.
 • WPF 큐는 ACCEPTED·DUPLICATE·REJECTED만 삭제, 그 밖의 상태·응답 누락·요청 실패는 보관 후 같은 resultId로 재전송.
 • [설계 35] 조회는 POST 단건(popup + deliveryId), 결과는 1건씩 순서대로 전송. 미종결 결과가 남으면 다음 조회를 미룸(장애 복구 정책 확정 전 임시 기준).
-• [설계 35] TEXT·IMAGE 닫기(CLOSE·LINK_AND_CLOSE)는 완료 처리. 설문·퀴즈·영상 미완료 결과는 저장 시각부터 pollingIntervalSeconds 동안 재노출 유예.</t>
+• [설계 35] TEXT·IMAGE 닫기(CLOSE·LINK_AND_CLOSE)는 완료 처리. 설문·퀴즈·영상 미완료 결과는 저장 시각부터 pollingIntervalSeconds 동안 재노출 유예.
+• [TODO52-2] popup.showLater(기본 false)로 Footer "나중에 보기" 표시, 누르면 resultType LATER. 완료·숨김 없이 다음 조회 주기에 다시 표시(HIDDEN·hideDays 의미 유지).</t>
         </is>
       </c>
       <c r="H36" s="173" t="n"/>
@@ -4127,7 +4128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="268" min="1" max="1"/>
@@ -5071,12 +5072,12 @@
     <row r="32" ht="22" customHeight="1" s="268">
       <c r="A32" s="666" t="inlineStr">
         <is>
-          <t>hideDays</t>
+          <t>showLater</t>
         </is>
       </c>
       <c r="B32" s="385" t="inlineStr">
         <is>
-          <t>popup.hideDays</t>
+          <t>popup.showLater</t>
         </is>
       </c>
       <c r="C32" s="385" t="inlineStr">
@@ -5086,17 +5087,17 @@
       </c>
       <c r="D32" s="385" t="inlineStr">
         <is>
-          <t>null → HIDDEN 시 30일</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E32" s="385" t="inlineStr">
         <is>
-          <t>숨김 일수(1~3650)</t>
+          <t>나중에 보기 버튼(Footer 표시 시)</t>
         </is>
       </c>
       <c r="F32" s="667" t="inlineStr">
         <is>
-          <t>Result HIDDEN의 hideDays 생성에 사용. 관리자 저장도 1~3650만 허용(설계 46)</t>
+          <t>모든 유형. 누르면 Result LATER(완료·숨김 없이 다음 조회 주기에 재표시). 완료 전 닫기 잠금 중에도 가능(TODO52-2)</t>
         </is>
       </c>
       <c r="G32" s="300" t="n"/>
@@ -5105,32 +5106,32 @@
     <row r="33" ht="22" customHeight="1" s="268">
       <c r="A33" s="666" t="inlineStr">
         <is>
-          <t>completionRatio</t>
+          <t>hideDays</t>
         </is>
       </c>
       <c r="B33" s="385" t="inlineStr">
         <is>
-          <t>popup.completionRatio</t>
+          <t>popup.hideDays</t>
         </is>
       </c>
       <c r="C33" s="385" t="inlineStr">
         <is>
-          <t>VIDEO/VIDEO+QUIZ</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D33" s="385" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>null → HIDDEN 시 30일</t>
         </is>
       </c>
       <c r="E33" s="385" t="inlineStr">
         <is>
-          <t>시청 완료 인정 비율</t>
+          <t>숨김 일수(1~3650)</t>
         </is>
       </c>
       <c r="F33" s="667" t="inlineStr">
         <is>
-          <t>0~1, content가 아님</t>
+          <t>Result HIDDEN의 hideDays 생성에 사용. 관리자 저장도 1~3650만 허용(설계 46)</t>
         </is>
       </c>
       <c r="G33" s="300" t="n"/>
@@ -5139,12 +5140,12 @@
     <row r="34" ht="22" customHeight="1" s="268">
       <c r="A34" s="666" t="inlineStr">
         <is>
-          <t>allowCloseBeforeComplete</t>
+          <t>completionRatio</t>
         </is>
       </c>
       <c r="B34" s="385" t="inlineStr">
         <is>
-          <t>popup.allowCloseBeforeComplete</t>
+          <t>popup.completionRatio</t>
         </is>
       </c>
       <c r="C34" s="385" t="inlineStr">
@@ -5154,17 +5155,17 @@
       </c>
       <c r="D34" s="385" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E34" s="385" t="inlineStr">
         <is>
-          <t>완료 전 종료 허용</t>
+          <t>시청 완료 인정 비율</t>
         </is>
       </c>
       <c r="F34" s="667" t="inlineStr">
         <is>
-          <t>content가 아님</t>
+          <t>0~1, content가 아님</t>
         </is>
       </c>
       <c r="G34" s="300" t="n"/>
@@ -5173,32 +5174,32 @@
     <row r="35" ht="22" customHeight="1" s="268">
       <c r="A35" s="666" t="inlineStr">
         <is>
-          <t>passingScore</t>
+          <t>allowCloseBeforeComplete</t>
         </is>
       </c>
       <c r="B35" s="385" t="inlineStr">
         <is>
-          <t>popup.passingScore</t>
+          <t>popup.allowCloseBeforeComplete</t>
         </is>
       </c>
       <c r="C35" s="385" t="inlineStr">
         <is>
-          <t>Y(QUIZ)</t>
+          <t>VIDEO/VIDEO+QUIZ</t>
         </is>
       </c>
       <c r="D35" s="385" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>true</t>
         </is>
       </c>
       <c r="E35" s="385" t="inlineStr">
         <is>
-          <t>합격 기준 점수</t>
+          <t>완료 전 종료 허용</t>
         </is>
       </c>
       <c r="F35" s="667" t="inlineStr">
         <is>
-          <t>채점 QUIZ는 반드시 명시</t>
+          <t>content가 아님</t>
         </is>
       </c>
       <c r="G35" s="300" t="n"/>
@@ -5207,101 +5208,131 @@
     <row r="36" ht="22" customHeight="1" s="268">
       <c r="A36" s="666" t="inlineStr">
         <is>
-          <t>questions[]</t>
+          <t>passingScore</t>
         </is>
       </c>
       <c r="B36" s="385" t="inlineStr">
         <is>
-          <t>popup.questions[]</t>
+          <t>popup.passingScore</t>
         </is>
       </c>
       <c r="C36" s="385" t="inlineStr">
         <is>
-          <t>Y(SURVEY/QUIZ)</t>
+          <t>Y(QUIZ)</t>
         </is>
       </c>
       <c r="D36" s="385" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="E36" s="385" t="inlineStr">
         <is>
-          <t>문항 목록</t>
-        </is>
-      </c>
-      <c r="F36" s="667" t="str"/>
+          <t>합격 기준 점수</t>
+        </is>
+      </c>
+      <c r="F36" s="667" t="inlineStr">
+        <is>
+          <t>채점 QUIZ는 반드시 명시</t>
+        </is>
+      </c>
       <c r="G36" s="300" t="n"/>
       <c r="H36" s="300" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1" s="268">
-      <c r="A37" s="756" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B37" s="757" t="inlineStr">
-        <is>
-          <t>popup.content</t>
-        </is>
-      </c>
-      <c r="C37" s="757" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D37" s="757" t="inlineStr">
-        <is>
-          <t>유형별 필수값</t>
-        </is>
-      </c>
-      <c r="E37" s="757" t="inlineStr">
-        <is>
-          <t>타입별 콘텐츠/전용 옵션 object</t>
-        </is>
-      </c>
-      <c r="F37" s="758" t="inlineStr">
-        <is>
-          <t>공통 UI 옵션은 더 이상 content에 넣지 않음</t>
-        </is>
-      </c>
+      <c r="A37" s="666" t="inlineStr">
+        <is>
+          <t>questions[]</t>
+        </is>
+      </c>
+      <c r="B37" s="385" t="inlineStr">
+        <is>
+          <t>popup.questions[]</t>
+        </is>
+      </c>
+      <c r="C37" s="385" t="inlineStr">
+        <is>
+          <t>Y(SURVEY/QUIZ)</t>
+        </is>
+      </c>
+      <c r="D37" s="385" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E37" s="385" t="inlineStr">
+        <is>
+          <t>문항 목록</t>
+        </is>
+      </c>
+      <c r="F37" s="667" t="str"/>
       <c r="G37" s="300" t="n"/>
       <c r="H37" s="300" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1" s="268">
-      <c r="A38" s="438" t="n"/>
-      <c r="B38" s="439" t="n"/>
-      <c r="C38" s="439" t="n"/>
-      <c r="D38" s="439" t="n"/>
-      <c r="E38" s="439" t="n"/>
-      <c r="F38" s="440" t="n"/>
+      <c r="A38" s="756" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="B38" s="757" t="inlineStr">
+        <is>
+          <t>popup.content</t>
+        </is>
+      </c>
+      <c r="C38" s="757" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D38" s="757" t="inlineStr">
+        <is>
+          <t>유형별 필수값</t>
+        </is>
+      </c>
+      <c r="E38" s="757" t="inlineStr">
+        <is>
+          <t>타입별 콘텐츠/전용 옵션 object</t>
+        </is>
+      </c>
+      <c r="F38" s="758" t="inlineStr">
+        <is>
+          <t>공통 UI 옵션은 더 이상 content에 넣지 않음</t>
+        </is>
+      </c>
       <c r="G38" s="300" t="n"/>
       <c r="H38" s="300" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1" s="268">
-      <c r="A39" s="862" t="inlineStr">
-        <is>
-          <t>popupPosition ENUM</t>
-        </is>
-      </c>
-      <c r="B39" s="913" t="n"/>
-      <c r="C39" s="913" t="n"/>
-      <c r="D39" s="913" t="n"/>
-      <c r="E39" s="913" t="n"/>
-      <c r="F39" s="913" t="n"/>
+      <c r="A39" s="438" t="n"/>
+      <c r="B39" s="439" t="n"/>
+      <c r="C39" s="439" t="n"/>
+      <c r="D39" s="439" t="n"/>
+      <c r="E39" s="439" t="n"/>
+      <c r="F39" s="440" t="n"/>
       <c r="G39" s="300" t="n"/>
       <c r="H39" s="300" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1" s="268">
-      <c r="A40" s="917" t="inlineStr">
-        <is>
-          <t>CENTER / TOP_LEFT / TOP_CENTER / TOP_RIGHT / CENTER_LEFT / CENTER_RIGHT / BOTTOM_LEFT / BOTTOM_CENTER / BOTTOM_RIGHT</t>
-        </is>
-      </c>
+      <c r="A40" s="862" t="inlineStr">
+        <is>
+          <t>popupPosition ENUM</t>
+        </is>
+      </c>
+      <c r="B40" s="913" t="n"/>
+      <c r="C40" s="913" t="n"/>
+      <c r="D40" s="913" t="n"/>
+      <c r="E40" s="913" t="n"/>
+      <c r="F40" s="913" t="n"/>
       <c r="G40" s="300" t="n"/>
       <c r="H40" s="300" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1" s="268">
+      <c r="A41" s="917" t="inlineStr">
+        <is>
+          <t>CENTER / TOP_LEFT / TOP_CENTER / TOP_RIGHT / CENTER_LEFT / CENTER_RIGHT / BOTTOM_LEFT / BOTTOM_CENTER / BOTTOM_RIGHT</t>
+        </is>
+      </c>
       <c r="G41" s="300" t="n"/>
       <c r="H41" s="300" t="n"/>
     </row>
@@ -5310,12 +5341,6 @@
       <c r="H42" s="300" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1" s="268">
-      <c r="A43" s="300" t="n"/>
-      <c r="B43" s="300" t="n"/>
-      <c r="C43" s="300" t="n"/>
-      <c r="D43" s="300" t="n"/>
-      <c r="E43" s="300" t="n"/>
-      <c r="F43" s="300" t="n"/>
       <c r="G43" s="300" t="n"/>
       <c r="H43" s="300" t="n"/>
     </row>
@@ -6489,7 +6514,16 @@
       <c r="G160" s="300" t="n"/>
       <c r="H160" s="300" t="n"/>
     </row>
-    <row r="161" ht="22" customHeight="1" s="268"/>
+    <row r="161" ht="22" customHeight="1" s="268">
+      <c r="A161" s="300" t="n"/>
+      <c r="B161" s="300" t="n"/>
+      <c r="C161" s="300" t="n"/>
+      <c r="D161" s="300" t="n"/>
+      <c r="E161" s="300" t="n"/>
+      <c r="F161" s="300" t="n"/>
+      <c r="G161" s="300" t="n"/>
+      <c r="H161" s="300" t="n"/>
+    </row>
     <row r="162" ht="22" customHeight="1" s="268"/>
     <row r="163" ht="22" customHeight="1" s="268"/>
     <row r="164" ht="22" customHeight="1" s="268"/>
@@ -6511,10 +6545,10 @@
     <row r="180" ht="22" customHeight="1" s="268"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A40:F42"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:F43"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14851,6 +14885,7 @@
   "backgroundOverlayOpacity": 0.45,
   "popupPosition": "CENTER",
   "showDoNotShowAgain": false,
+  "showLater": false,
   "questions": [],
   "content": {
     "plainText": "점검 공지\n서비스 점검이 진행됩니다.",
@@ -15857,7 +15892,7 @@
       </c>
       <c r="F11" s="385" t="inlineStr">
         <is>
-          <t>CLOSED / HIDDEN / SUBMITTED / VIDEO_WATCHED</t>
+          <t>CLOSED / HIDDEN / LATER / SUBMITTED / VIDEO_WATCHED</t>
         </is>
       </c>
       <c r="G11" s="667" t="inlineStr">
@@ -16395,9 +16430,10 @@
         <is>
           <t>CLOSED: 일반 종료
 HIDDEN: 다시 보지 않기 선택
+LATER: 나중에 보기 버튼(TODO52-2). 모든 유형, 완료·숨김 없이 다음 조회 주기(pollingIntervalSeconds 유예 후) 재표시. hideDays·answers·video 미포함
 SUBMITTED: SURVEY / QUIZ / VIDEO+QUIZ 정상 제출
 VIDEO_WATCHED: 단독 VIDEO 종료 또는 VIDEO+QUIZ를 제출하지 않고 종료한 경우 영상 시청 결과
-※ 우선순위: 다시 보지 않기를 선택하면 영상 시청 기록이 있어도 HIDDEN
+※ 우선순위: 다시 보지 않기를 선택하면 영상 시청 기록이 있어도 HIDDEN. 단 나중에 보기 버튼으로 닫으면 체크 여부와 관계없이 LATER(영상 시청 정보 미전송, 기존 기록 유지)
 ※ responseStartedAt은 삭제됨. displayedAt과 동일값이어서 중복이었음.
 ※ 결과는 먼저 로컬 pending-results에 저장하고, 저장된 순서대로 1건씩 전송. 통신 실패 시 같은 resultId로 재전송.
 ※ [설계 35] TEXT·IMAGE의 CLOSED(Footer 닫기·바로가기 포함)는 완료로 저장. 설문·퀴즈·영상이 미완료로 끝나면 조회 간격 동안 재노출 유예.</t>

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -5097,7 +5097,7 @@
       </c>
       <c r="F32" s="667" t="inlineStr">
         <is>
-          <t>모든 유형. 누르면 Result LATER(완료·숨김 없이 다음 조회 주기에 재표시). 완료 전 닫기 잠금 중에도 가능(TODO52-2)</t>
+          <t>모든 유형. 누르면 Result LATER(완료·숨김 없이 다음 조회 주기에 재표시). 완료 기준 전에도 가능(TODO52-2), 완료 기준 전 유일한 화면 이탈 버튼(TODO57)</t>
         </is>
       </c>
       <c r="G32" s="300" t="n"/>
@@ -5184,22 +5184,22 @@
       </c>
       <c r="C35" s="385" t="inlineStr">
         <is>
-          <t>VIDEO/VIDEO+QUIZ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D35" s="385" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" s="385" t="inlineStr">
         <is>
-          <t>완료 전 종료 허용</t>
+          <t>폐기</t>
         </is>
       </c>
       <c r="F35" s="667" t="inlineStr">
         <is>
-          <t>content가 아님</t>
+          <t>폐기(TODO57). 응답에서 제거, 새 WPF는 보내도 무시. 화면 버튼=completionRatio, 외부 닫기=content.useBackgroundOverlay, 완료 전 연기=showLater. 구 WPF는 필드 누락 시 true로 동작</t>
         </is>
       </c>
       <c r="G35" s="300" t="n"/>
@@ -6545,9 +6545,9 @@
     <row r="180" ht="22" customHeight="1" s="268"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A41:F43"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10923,22 +10923,22 @@
       </c>
       <c r="C18" s="668" t="inlineStr">
         <is>
-          <t>VIDEO/VIDEO+QUIZ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D18" s="668" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" s="668" t="inlineStr">
         <is>
-          <t>완료 전 종료 허용</t>
+          <t>폐기</t>
         </is>
       </c>
       <c r="F18" s="669" t="inlineStr">
         <is>
-          <t>최상위</t>
+          <t>폐기(TODO57). 응답에서 제거, 새 WPF는 보내도 무시. 화면 버튼=completionRatio, 외부 닫기=content.useBackgroundOverlay, 완료 전 연기=showLater. 구 WPF는 필드 누락 시 true로 동작</t>
         </is>
       </c>
       <c r="G18" s="300" t="n"/>
@@ -10962,7 +10962,7 @@
 • 두 경로 모두 공통 WPF Overlay 컨트롤바 사용, Chromium 기본 controls는 사용하지 않음.
 • allowSeek=false면 seek만 차단하고 진행률/시간 표시는 유지.
 • 시청 완료 판단은 min(watchedSeconds, durationSeconds) / durationSeconds를 소수점 4자리에서 내린 비율 기준이며(서버·VIDEO+QUIZ 동일, 설계 53-16) 탐색한 구간은 watchedSeconds에 합산하지 않음.
-• completionRatio / allowCloseBeforeComplete는 content가 아니라 popup 최상위.
+• completionRatio는 content가 아니라 popup 최상위(allowCloseBeforeComplete는 TODO57에서 폐기 — 시청 기준 전 닫기 버튼 항상 비활성, 외부 닫기는 Overlay, 연기는 나중에 보기).
 • YouTube iframe 지원은 제거됨.</t>
         </is>
       </c>
@@ -13559,17 +13559,17 @@
       </c>
       <c r="D37" s="757" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" s="757" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" s="757" t="inlineStr">
         <is>
-          <t>시청 기준 전 종료 허용</t>
+          <t>폐기(TODO57). 시청 기준 전 이탈은 showLater, 외부 닫기는 Overlay</t>
         </is>
       </c>
       <c r="G37" s="758" t="inlineStr">
@@ -15163,7 +15163,6 @@
   "title": "보안 교육",
   "footerAction": "CLOSE",
   "completionRatio": 0.8,
-  "allowCloseBeforeComplete": false,
   "questions": [],
   "content": {
     "videoUrl": "https://example.com/media/security.mp4",
@@ -15488,7 +15487,6 @@
   "title": "영상 교육 및 확인 퀴즈",
   "footerAction": "SUBMIT",
   "completionRatio": 0.8,
-  "allowCloseBeforeComplete": true,
   "passingScore": 80,
   "questions": [
     {

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -3459,7 +3459,7 @@
       </c>
       <c r="D19" s="667" t="inlineStr">
         <is>
-          <t>일반 IMAGE 크기는 content.width/height</t>
+          <t>IMAGE 크기도 공통 popup.width/height(FIT_TO_IMAGE는 이미지 콘텐츠 영역, TODO58)</t>
         </is>
       </c>
       <c r="E19" s="913" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="C12" s="385" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="D12" s="385" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="F12" s="667" t="inlineStr">
         <is>
-          <t>일반 IMAGE는 content.width 사용</t>
+          <t>IMAGE: ADAPTIVE·ORIGINAL 창 전체, FIT_TO_IMAGE 이미지 콘텐츠 영역 너비. 일반 IMAGE는 생략 가능(원본 기준). content.width 폐기(TODO58)</t>
         </is>
       </c>
       <c r="G12" s="300" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C13" s="385" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="D13" s="385" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="F13" s="667" t="inlineStr">
         <is>
-          <t>일반 IMAGE는 content.height 사용</t>
+          <t>IMAGE: ADAPTIVE·ORIGINAL 창 전체, FIT_TO_IMAGE 이미지 콘텐츠 영역 높이. 일반 IMAGE는 생략 가능(원본 기준). content.height 폐기(TODO58)</t>
         </is>
       </c>
       <c r="G13" s="300" t="n"/>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="B11" s="385" t="inlineStr">
         <is>
-          <t>popup.content.width</t>
+          <t>popup.width</t>
         </is>
       </c>
       <c r="C11" s="385" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="E11" s="385" t="inlineStr">
         <is>
-          <t>ADAPTIVE 창 크기 / FIT_TO_IMAGE 이미지 DIP</t>
+          <t>최상위 값(TODO58). ADAPTIVE·ORIGINAL 창 전체 / FIT_TO_IMAGE 이미지 콘텐츠 영역. content.width/height 폐기</t>
         </is>
       </c>
       <c r="F11" s="667" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B12" s="385" t="inlineStr">
         <is>
-          <t>popup.content.height</t>
+          <t>popup.height</t>
         </is>
       </c>
       <c r="C12" s="385" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="E12" s="385" t="inlineStr">
         <is>
-          <t>ADAPTIVE 창 크기 / FIT_TO_IMAGE 이미지 DIP</t>
+          <t>최상위 값(TODO58). ADAPTIVE·ORIGINAL 창 전체 / FIT_TO_IMAGE 이미지 콘텐츠 영역. content.width/height 폐기</t>
         </is>
       </c>
       <c r="F12" s="667" t="inlineStr">
@@ -8974,11 +8974,11 @@
     <row r="16" ht="22" customHeight="1" s="268">
       <c r="A16" s="678" t="inlineStr">
         <is>
-          <t>크기 모드
-• ADAPTIVE: 창 우선, 이미지 비율 유지.
-• FIT_TO_IMAGE: 이미지 표시 DIP 크기 우선. keepAspectRatio=true 기본.
-• ORIGINAL: 최상위 width/height를 창 크기로 사용하고 왼쪽 위 기준 Clip.
-• 일반 IMAGE는 최상위 width/height 대신 content.width/height 사용.
+          <t>크기 모드(TODO58 — 크기는 최상위 width/height 한 쌍)
+• ADAPTIVE: width/height = 팝업 창 전체. 헤더·푸터·제목·설명·여백을 뺀 영역에 이미지 비율 유지.
+• FIT_TO_IMAGE: width/height = 이미지 콘텐츠 영역. 부가 영역을 더해 창 계산. keepAspectRatio=true(기본)는 영역 안 비율 유지(여백 가능), false는 영역 채움.
+• ORIGINAL: width/height = 팝업 창 전체. 왼쪽 위 기준 원본 크기, 넘치는 부분 Clip.
+• content.width/height는 폐기. 새 WPF는 최상위 값이 없을 때만 구 서버 content 값을 임시로 읽음.
 • IMAGE 창 최대는 현재 모니터 작업 영역의 90%.</t>
         </is>
       </c>

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -3795,7 +3795,9 @@
 • WPF 큐는 ACCEPTED·DUPLICATE·REJECTED만 삭제, 그 밖의 상태·응답 누락·요청 실패는 보관 후 같은 resultId로 재전송.
 • [설계 35] 조회는 POST 단건(popup + deliveryId), 결과는 1건씩 순서대로 전송. 미종결 결과가 남으면 다음 조회를 미룸(장애 복구 정책 확정 전 임시 기준).
 • [설계 35] TEXT·IMAGE 닫기(CLOSE·LINK_AND_CLOSE)는 완료 처리. 설문·퀴즈·영상 미완료 결과는 저장 시각부터 pollingIntervalSeconds 동안 재노출 유예.
-• [TODO52-2] popup.showLater(기본 false)로 Footer "나중에 보기" 표시, 누르면 resultType LATER. 완료·숨김 없이 다음 조회 주기에 다시 표시(HIDDEN·hideDays 의미 유지).</t>
+• [TODO52-2] popup.showLater(기본 false)로 Footer "나중에 보기" 표시, 누르면 resultType LATER. 완료·숨김 없이 다음 조회 주기에 다시 표시(HIDDEN·hideDays 의미 유지).
+• [TODO63] textBlocks[].indent 5단계 제한 해제(0 이상 정수, 1단계 40 유지). TEXT·SURVEY·QUIZ 서식 필드 공통.
+• [TODO52-5] QUIZ MULTIPLE_CHOICE는 isCorrect=true 선택지 수까지만 선택 가능(새 필드 없음).</t>
         </is>
       </c>
       <c r="H36" s="173" t="n"/>
@@ -6778,12 +6780,12 @@
       </c>
       <c r="E9" s="385" t="inlineStr">
         <is>
-          <t>문단 왼쪽 들여쓰기 단계(0~5 정수)</t>
+          <t>문단 왼쪽 들여쓰기 단계(0 이상 정수, 단계 수 제한 없음·2147483647 이하)</t>
         </is>
       </c>
       <c r="F9" s="667" t="inlineStr">
         <is>
-          <t>1단계=40(웹 CSS px·WPF DIP) 누적, 줄바꿈된 모든 줄에 같은 여백(설계 49). plainText에 공백·탭 넣지 않음. 서버 저장 시 0~5만 허용</t>
+          <t>1단계=40(웹 CSS px·WPF DIP) 누적, 줄바꿈된 모든 줄에 같은 여백(설계 49). plainText에 공백·탭 넣지 않음. 서버 저장 시 0 이상 정수만 허용(TODO63, 5단계 제한 해제)</t>
         </is>
       </c>
       <c r="G9" s="300" t="n"/>
@@ -7245,7 +7247,7 @@
 • 통합 전 행은 조회 시 제목(LEFT·굵게·24)→설명→본문 순으로 합친다. showContentHeader=false였던 행은 합치지 않는다.
 • 헤더 표시·본문 숨김(showPlainText=false)이던 행은 헤더만 보이기: 제목·설명 문단만 보내고 숨긴 본문은 빼며 showPlainText=true(설계 39). 관리자 재저장 시 숨긴 본문 삭제.
 • 공통 Overlay/Position/Font/Footer 옵션은 popup 최상위에서 받음.
-• 허용 정책은 서버 저장 API가 검증하고 WPF는 표시 방어만 함(설계 48): 크기 1~200 밖·들여쓰기 여백 400 초과는 기본값/0, 변환 실패 색·미매핑 글꼴·알 수 없는 정렬은 기본값, 서식 값 타입 오류는 그 값만 기본값, 구조 오류는 plainText 표시.</t>
+• 허용 정책은 서버 저장 API가 검증하고 WPF는 표시 방어만 함(설계 48): 크기 1~200 밖·들여쓰기 소수·음수·범위 초과는 0(단계 수 제한 없음, TODO63), 변환 실패 색·미매핑 글꼴·알 수 없는 정렬은 기본값, 서식 값 타입 오류는 그 값만 기본값, 구조 오류는 plainText 표시.</t>
         </is>
       </c>
       <c r="G25" s="300" t="n"/>
@@ -12643,7 +12645,7 @@
       </c>
       <c r="F10" s="385" t="inlineStr">
         <is>
-          <t>SINGLE_CHOICE / MULTIPLE_CHOICE / TEXT</t>
+          <t>SINGLE_CHOICE / MULTIPLE_CHOICE / TEXT. QUIZ MULTIPLE_CHOICE는 isCorrect=true 선택지 수까지만 선택 가능(TODO52-5)</t>
         </is>
       </c>
       <c r="G10" s="667" t="str"/>
@@ -13041,7 +13043,7 @@
       </c>
       <c r="F21" s="385" t="inlineStr">
         <is>
-          <t>정답 여부</t>
+          <t>정답 여부. QUIZ MULTIPLE_CHOICE의 true 개수 = 응답자 최대 선택 수(TODO52-5)</t>
         </is>
       </c>
       <c r="G21" s="667" t="inlineStr">
@@ -13595,6 +13597,7 @@
           <t>채점/제출 동작
 • SURVEY는 채점하지 않음.
 • 선택형 QUIZ는 선택 optionId 집합과 isCorrect=true 집합이 정확히 같을 때 정답, 부분 점수 없음.
+• [TODO52-5] QUIZ MULTIPLE_CHOICE는 정답 수까지만 선택 가능. 한도 도달 시 남은 선택지 비활성·"최대 N개 선택" 안내(WPF·관리자 미리보기 동일, 추가 필드 없음). SURVEY 복수 선택은 제한 없음.
 • TEXT QUIZ는 correctAnswer + EXACT/CONTAINS 사용 가능.
 • WPF가 score/passed를 최종 판정하고 통과한 QUIZ만 SUBMITTED 전송.
 • VIDEO+QUIZ는 watchedSeconds / durationSeconds(소수점 4자리 내림)가 completionRatio 이상일 때 퀴즈 입력/제출 활성화.

--- a/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
+++ b/docs/interfaces/WPF_POPUP_INTERFACE_LATEST_MAIN.xlsx
@@ -3797,7 +3797,8 @@
 • [설계 35] TEXT·IMAGE 닫기(CLOSE·LINK_AND_CLOSE)는 완료 처리. 설문·퀴즈·영상 미완료 결과는 저장 시각부터 pollingIntervalSeconds 동안 재노출 유예.
 • [TODO52-2] popup.showLater(기본 false)로 Footer "나중에 보기" 표시, 누르면 resultType LATER. 완료·숨김 없이 다음 조회 주기에 다시 표시(HIDDEN·hideDays 의미 유지).
 • [TODO63] textBlocks[].indent 5단계 제한 해제(0 이상 정수, 1단계 40 유지). TEXT·SURVEY·QUIZ 서식 필드 공통.
-• [TODO52-5] QUIZ MULTIPLE_CHOICE는 isCorrect=true 선택지 수까지만 선택 가능(새 필드 없음).</t>
+• [TODO52-5] QUIZ MULTIPLE_CHOICE는 isCorrect=true 선택지 수까지만 선택 가능(새 필드 없음).
+• [TODO52-1] 게시 기간 안 노출 요일·시간대는 서버가 KST로 판단해 후보에서 거름(WPF 응답·결과 계약 변경 없음, 요일·시간대 미포함).</t>
         </is>
       </c>
       <c r="H36" s="173" t="n"/>
